--- a/벤츠_models.xlsx
+++ b/벤츠_models.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -116,6 +116,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -685,7 +688,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>2014년식 FBS3·FBS4 자료 상충 — VIN(SA코드 803/804) 확인</t>
+          <t>2014년식 FBS3·FBS4 전환 월 자료 없음(미국형은 2014부터 FBS4) — VIN(SA코드 803/804) 확인</t>
         </is>
       </c>
     </row>
@@ -1245,10 +1248,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -1271,17 +1274,13 @@
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1383,7 +1382,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2014년식 FBS3·FBS4 자료 상충 — VIN 확인</t>
+          <t>2014년식 FBS3·FBS4 전환 월 자료 없음(미국형은 2014부터 FBS4) — VIN(SA코드 803/804) 확인</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1618,10 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -1645,7 +1644,7 @@
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -1655,11 +1654,7 @@
           <t>auto-keys.eu(A45 AMG FBS4 키 — 미국형 315MHz 품번 제외), carsine</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1785,10 +1780,10 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -1811,7 +1806,7 @@
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -1821,11 +1816,7 @@
           <t>auto-keys.eu(A45 AMG FBS4 키 — 미국형 315MHz 품번 제외), carsine</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1843,10 +1834,10 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -1869,7 +1860,7 @@
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -1879,11 +1870,7 @@
           <t>auto-keys.eu(A45 AMG FBS4 키 — 미국형 315MHz 품번 제외), carsine</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -1901,10 +1888,10 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -1927,7 +1914,7 @@
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -1937,11 +1924,7 @@
           <t>auto-keys.eu(A45 AMG FBS4 키 — 미국형 315MHz 품번 제외), carsine</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -1959,10 +1942,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -1985,7 +1968,7 @@
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -1995,11 +1978,7 @@
           <t>auto-keys.eu(A45 AMG FBS4 키 — 미국형 315MHz 품번 제외), carsine</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -2017,10 +1996,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -2043,7 +2022,7 @@
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -2053,11 +2032,7 @@
           <t>auto-keys.eu(A45 AMG FBS4 키 — 미국형 315MHz 품번 제외), carsine</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -2209,7 +2184,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>W246 FBS4 전환 시점 자료 없음 — 2014년식은 FBS3·FBS4 혼재 가능</t>
+          <t>W246 FBS4 EZS는 2015년 이후 표기 — 2014년식 FBS3·FBS4 혼재 가능, VIN 확인</t>
         </is>
       </c>
     </row>
@@ -3423,10 +3398,10 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -3445,7 +3420,7 @@
       <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="7" t="n"/>
       <c r="M55" s="7" t="inlineStr"/>
-      <c r="N55" s="4" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -3455,11 +3430,7 @@
           <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
         </is>
       </c>
-      <c r="P55" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
@@ -3477,10 +3448,10 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -3499,7 +3470,7 @@
       <c r="K56" s="7" t="inlineStr"/>
       <c r="L56" s="7" t="n"/>
       <c r="M56" s="7" t="inlineStr"/>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -3509,11 +3480,7 @@
           <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
         </is>
       </c>
-      <c r="P56" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -3531,10 +3498,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -3553,7 +3520,7 @@
       <c r="K57" s="7" t="inlineStr"/>
       <c r="L57" s="7" t="n"/>
       <c r="M57" s="7" t="inlineStr"/>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -3563,11 +3530,7 @@
           <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
         </is>
       </c>
-      <c r="P57" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -3585,10 +3548,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="D58" s="3" t="n"/>
+      <c r="E58" s="3" t="n"/>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -3607,7 +3570,7 @@
       <c r="K58" s="7" t="inlineStr"/>
       <c r="L58" s="7" t="n"/>
       <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="N58" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -3617,11 +3580,7 @@
           <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
         </is>
       </c>
-      <c r="P58" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -4039,12 +3998,12 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>FBS4, FBS3</t>
+      <c r="D67" s="3" t="n"/>
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>FBS4</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
@@ -4065,7 +4024,7 @@
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr"/>
-      <c r="N67" s="4" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -4075,11 +4034,7 @@
           <t>obdii365(205 전 연식 FBS4), tlkeys(W205 2015.4부터 FBS4·초기 생산 FBS3 요약), auto-keys.eu(A2059050600 434MHz FBS4)</t>
         </is>
       </c>
-      <c r="P67" s="4" t="inlineStr">
-        <is>
-          <t>W205 초기 생산분 FBS3 여부 자료 상충 — VIN 확인</t>
-        </is>
-      </c>
+      <c r="P67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -4097,12 +4052,12 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>FBS4, FBS3</t>
+      <c r="D68" s="3" t="n"/>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>FBS4</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
@@ -4123,7 +4078,7 @@
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="N68" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -4133,11 +4088,7 @@
           <t>obdii365(205 전 연식 FBS4), tlkeys(W205 2015.4부터 FBS4·초기 생산 FBS3 요약), auto-keys.eu(A2059050600 434MHz FBS4)</t>
         </is>
       </c>
-      <c r="P68" s="4" t="inlineStr">
-        <is>
-          <t>W205 초기 생산분 FBS3 여부 자료 상충 — VIN 확인</t>
-        </is>
-      </c>
+      <c r="P68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -6071,10 +6022,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" s="3" t="inlineStr"/>
-      <c r="G105" s="4" t="inlineStr">
+      <c r="D105" s="3" t="n"/>
+      <c r="E105" s="3" t="n"/>
+      <c r="F105" s="3" t="n"/>
+      <c r="G105" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -6093,7 +6044,7 @@
       <c r="K105" s="7" t="inlineStr"/>
       <c r="L105" s="7" t="n"/>
       <c r="M105" s="7" t="inlineStr"/>
-      <c r="N105" s="4" t="inlineStr">
+      <c r="N105" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -6103,11 +6054,7 @@
           <t>fcpeuro·batteriesplus(C63 W206 키) — W206 공통</t>
         </is>
       </c>
-      <c r="P105" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P105" s="10" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -7519,10 +7466,10 @@
           <t>2024(단종)</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr"/>
-      <c r="E133" s="3" t="inlineStr"/>
-      <c r="F133" s="3" t="inlineStr"/>
-      <c r="G133" s="4" t="inlineStr">
+      <c r="D133" s="3" t="n"/>
+      <c r="E133" s="3" t="n"/>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -7541,7 +7488,7 @@
       <c r="K133" s="7" t="inlineStr"/>
       <c r="L133" s="7" t="n"/>
       <c r="M133" s="7" t="inlineStr"/>
-      <c r="N133" s="4" t="inlineStr">
+      <c r="N133" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -7551,11 +7498,7 @@
           <t>W213 연식 기준</t>
         </is>
       </c>
-      <c r="P133" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P133" s="10" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="inlineStr">
@@ -9789,10 +9732,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D176" s="3" t="inlineStr"/>
-      <c r="E176" s="3" t="inlineStr"/>
-      <c r="F176" s="3" t="inlineStr"/>
-      <c r="G176" s="4" t="inlineStr">
+      <c r="D176" s="3" t="n"/>
+      <c r="E176" s="3" t="n"/>
+      <c r="F176" s="3" t="n"/>
+      <c r="G176" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -9811,7 +9754,7 @@
       <c r="K176" s="7" t="inlineStr"/>
       <c r="L176" s="7" t="n"/>
       <c r="M176" s="7" t="inlineStr"/>
-      <c r="N176" s="4" t="inlineStr">
+      <c r="N176" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -9821,11 +9764,7 @@
           <t>mbworld(2025 E53 키-프로필 연동), autoevolution(E53 W214)</t>
         </is>
       </c>
-      <c r="P176" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P176" s="10" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
@@ -11365,12 +11304,12 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="D206" s="3" t="inlineStr"/>
-      <c r="E206" s="3" t="inlineStr"/>
-      <c r="F206" s="3" t="inlineStr"/>
-      <c r="G206" s="4" t="inlineStr">
-        <is>
-          <t>FBS3[추정]</t>
+      <c r="D206" s="3" t="n"/>
+      <c r="E206" s="3" t="n"/>
+      <c r="F206" s="3" t="n"/>
+      <c r="G206" s="10" t="inlineStr">
+        <is>
+          <t>FBS3</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr">
@@ -11387,7 +11326,7 @@
       <c r="K206" s="7" t="inlineStr"/>
       <c r="L206" s="7" t="inlineStr"/>
       <c r="M206" s="7" t="inlineStr"/>
-      <c r="N206" s="4" t="inlineStr">
+      <c r="N206" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -11397,11 +11336,7 @@
           <t>wikipedia·autoevolution(W221 2005.8 생산, 2006년형으로 판매)</t>
         </is>
       </c>
-      <c r="P206" s="4" t="inlineStr">
-        <is>
-          <t>W221 2005.8 생산 — 2005년식 국내 판매분은 W220일 가능성, 초기형 키 방식 자료 없음</t>
-        </is>
-      </c>
+      <c r="P206" s="10" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
@@ -12501,10 +12436,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D228" s="3" t="inlineStr"/>
-      <c r="E228" s="3" t="inlineStr"/>
-      <c r="F228" s="3" t="inlineStr"/>
-      <c r="G228" s="4" t="inlineStr">
+      <c r="D228" s="3" t="n"/>
+      <c r="E228" s="3" t="n"/>
+      <c r="F228" s="3" t="n"/>
+      <c r="G228" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -12523,17 +12458,13 @@
       <c r="K228" s="7" t="inlineStr"/>
       <c r="L228" s="7" t="n"/>
       <c r="M228" s="7" t="inlineStr"/>
-      <c r="N228" s="4" t="inlineStr">
+      <c r="N228" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
       </c>
       <c r="O228" s="7" t="inlineStr"/>
-      <c r="P228" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P228" s="10" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
@@ -14309,10 +14240,10 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="D262" s="3" t="inlineStr"/>
-      <c r="E262" s="3" t="inlineStr"/>
-      <c r="F262" s="3" t="inlineStr"/>
-      <c r="G262" s="4" t="inlineStr">
+      <c r="D262" s="3" t="n"/>
+      <c r="E262" s="3" t="n"/>
+      <c r="F262" s="3" t="n"/>
+      <c r="G262" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -14331,7 +14262,7 @@
       <c r="K262" s="7" t="inlineStr"/>
       <c r="L262" s="7" t="n"/>
       <c r="M262" s="7" t="inlineStr"/>
-      <c r="N262" s="4" t="inlineStr">
+      <c r="N262" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -14341,11 +14272,7 @@
           <t>mbworld(2024 S63e 디지털 키 — 2025 NTG7부터 지원)</t>
         </is>
       </c>
-      <c r="P262" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P262" s="10" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
@@ -14513,10 +14440,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D266" s="3" t="inlineStr"/>
-      <c r="E266" s="3" t="inlineStr"/>
-      <c r="F266" s="3" t="inlineStr"/>
-      <c r="G266" s="4" t="inlineStr">
+      <c r="D266" s="3" t="n"/>
+      <c r="E266" s="3" t="n"/>
+      <c r="F266" s="3" t="n"/>
+      <c r="G266" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -14535,7 +14462,7 @@
       <c r="K266" s="7" t="inlineStr"/>
       <c r="L266" s="7" t="n"/>
       <c r="M266" s="7" t="inlineStr"/>
-      <c r="N266" s="4" t="inlineStr">
+      <c r="N266" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -14545,11 +14472,7 @@
           <t>mbworld(2024 S63e 디지털 키 — 2025 NTG7부터 지원)</t>
         </is>
       </c>
-      <c r="P266" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P266" s="10" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
@@ -15241,10 +15164,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D280" s="3" t="inlineStr"/>
-      <c r="E280" s="3" t="inlineStr"/>
-      <c r="F280" s="3" t="inlineStr"/>
-      <c r="G280" s="4" t="inlineStr">
+      <c r="D280" s="3" t="n"/>
+      <c r="E280" s="3" t="n"/>
+      <c r="F280" s="3" t="n"/>
+      <c r="G280" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -15263,7 +15186,7 @@
       <c r="K280" s="7" t="inlineStr"/>
       <c r="L280" s="7" t="n"/>
       <c r="M280" s="7" t="inlineStr"/>
-      <c r="N280" s="4" t="inlineStr">
+      <c r="N280" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -15273,11 +15196,7 @@
           <t>auto-data(H247 FL 2023), mbworld</t>
         </is>
       </c>
-      <c r="P280" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P280" s="10" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
@@ -15815,10 +15734,10 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D291" s="3" t="inlineStr"/>
-      <c r="E291" s="3" t="inlineStr"/>
-      <c r="F291" s="3" t="inlineStr"/>
-      <c r="G291" s="4" t="inlineStr">
+      <c r="D291" s="3" t="n"/>
+      <c r="E291" s="3" t="n"/>
+      <c r="F291" s="3" t="n"/>
+      <c r="G291" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -15837,7 +15756,7 @@
       <c r="K291" s="7" t="inlineStr"/>
       <c r="L291" s="7" t="n"/>
       <c r="M291" s="7" t="inlineStr"/>
-      <c r="N291" s="4" t="inlineStr">
+      <c r="N291" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -15847,11 +15766,7 @@
           <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35)</t>
         </is>
       </c>
-      <c r="P291" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P291" s="10" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="7" t="inlineStr">
@@ -15869,10 +15784,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D292" s="3" t="inlineStr"/>
-      <c r="E292" s="3" t="inlineStr"/>
-      <c r="F292" s="3" t="inlineStr"/>
-      <c r="G292" s="4" t="inlineStr">
+      <c r="D292" s="3" t="n"/>
+      <c r="E292" s="3" t="n"/>
+      <c r="F292" s="3" t="n"/>
+      <c r="G292" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -15891,7 +15806,7 @@
       <c r="K292" s="7" t="inlineStr"/>
       <c r="L292" s="7" t="n"/>
       <c r="M292" s="7" t="inlineStr"/>
-      <c r="N292" s="4" t="inlineStr">
+      <c r="N292" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -15901,11 +15816,7 @@
           <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35)</t>
         </is>
       </c>
-      <c r="P292" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P292" s="10" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
@@ -15923,10 +15834,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D293" s="3" t="inlineStr"/>
-      <c r="E293" s="3" t="inlineStr"/>
-      <c r="F293" s="3" t="inlineStr"/>
-      <c r="G293" s="4" t="inlineStr">
+      <c r="D293" s="3" t="n"/>
+      <c r="E293" s="3" t="n"/>
+      <c r="F293" s="3" t="n"/>
+      <c r="G293" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -15945,7 +15856,7 @@
       <c r="K293" s="7" t="inlineStr"/>
       <c r="L293" s="7" t="n"/>
       <c r="M293" s="7" t="inlineStr"/>
-      <c r="N293" s="4" t="inlineStr">
+      <c r="N293" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -15955,11 +15866,7 @@
           <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35)</t>
         </is>
       </c>
-      <c r="P293" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P293" s="10" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="7" t="inlineStr">
@@ -16277,10 +16184,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D300" s="3" t="inlineStr"/>
-      <c r="E300" s="3" t="inlineStr"/>
-      <c r="F300" s="3" t="inlineStr"/>
-      <c r="G300" s="4" t="inlineStr">
+      <c r="D300" s="3" t="n"/>
+      <c r="E300" s="3" t="n"/>
+      <c r="F300" s="3" t="n"/>
+      <c r="G300" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -16299,7 +16206,7 @@
       <c r="K300" s="7" t="inlineStr"/>
       <c r="L300" s="7" t="n"/>
       <c r="M300" s="7" t="inlineStr"/>
-      <c r="N300" s="4" t="inlineStr">
+      <c r="N300" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -16309,11 +16216,7 @@
           <t>autoevolution(2024 GLB35 FL), mbusa(2023 GLB250 keyless)</t>
         </is>
       </c>
-      <c r="P300" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P300" s="10" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
@@ -16581,10 +16484,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D306" s="3" t="inlineStr"/>
-      <c r="E306" s="3" t="inlineStr"/>
-      <c r="F306" s="3" t="inlineStr"/>
-      <c r="G306" s="4" t="inlineStr">
+      <c r="D306" s="3" t="n"/>
+      <c r="E306" s="3" t="n"/>
+      <c r="F306" s="3" t="n"/>
+      <c r="G306" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -16603,7 +16506,7 @@
       <c r="K306" s="7" t="inlineStr"/>
       <c r="L306" s="7" t="n"/>
       <c r="M306" s="7" t="inlineStr"/>
-      <c r="N306" s="4" t="inlineStr">
+      <c r="N306" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -16613,11 +16516,7 @@
           <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL)</t>
         </is>
       </c>
-      <c r="P306" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P306" s="10" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
@@ -16935,12 +16834,12 @@
           <t>2015(단종)</t>
         </is>
       </c>
-      <c r="D313" s="3" t="inlineStr"/>
-      <c r="E313" s="3" t="inlineStr"/>
-      <c r="F313" s="3" t="inlineStr"/>
-      <c r="G313" s="4" t="inlineStr">
-        <is>
-          <t>FBS3, FBS4</t>
+      <c r="D313" s="3" t="n"/>
+      <c r="E313" s="3" t="n"/>
+      <c r="F313" s="3" t="n"/>
+      <c r="G313" s="10" t="inlineStr">
+        <is>
+          <t>FBS3[2015 초기 생산], FBS4[2015 후기 생산]</t>
         </is>
       </c>
       <c r="H313" s="7" t="inlineStr">
@@ -16957,7 +16856,7 @@
       <c r="K313" s="7" t="inlineStr"/>
       <c r="L313" s="7" t="inlineStr"/>
       <c r="M313" s="7" t="inlineStr"/>
-      <c r="N313" s="4" t="inlineStr">
+      <c r="N313" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -16967,11 +16866,7 @@
           <t>the-ecu-pro(2015 GLK350 EIS FBS4), northcoastkeyless(2009-2015 GLK IYZDC 키)</t>
         </is>
       </c>
-      <c r="P313" s="4" t="inlineStr">
-        <is>
-          <t>2015년식 FBS3·FBS4 혼재 — X204는 FBS4 적용 목록에 없음, 전환 월 미확인</t>
-        </is>
-      </c>
+      <c r="P313" s="10" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="7" t="inlineStr">
@@ -18045,10 +17940,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D334" s="3" t="inlineStr"/>
-      <c r="E334" s="3" t="inlineStr"/>
-      <c r="F334" s="3" t="inlineStr"/>
-      <c r="G334" s="4" t="inlineStr">
+      <c r="D334" s="3" t="n"/>
+      <c r="E334" s="3" t="n"/>
+      <c r="F334" s="3" t="n"/>
+      <c r="G334" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -18067,7 +17962,7 @@
       <c r="K334" s="7" t="inlineStr"/>
       <c r="L334" s="7" t="n"/>
       <c r="M334" s="7" t="inlineStr"/>
-      <c r="N334" s="4" t="inlineStr">
+      <c r="N334" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -18077,11 +17972,7 @@
           <t>mbusa(2025 AMG GLC63 S E), mbworld(X254 디지털 키)</t>
         </is>
       </c>
-      <c r="P334" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P334" s="10" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
@@ -18099,12 +17990,12 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="D335" s="3" t="inlineStr"/>
-      <c r="E335" s="3" t="inlineStr"/>
-      <c r="F335" s="3" t="inlineStr"/>
-      <c r="G335" s="4" t="inlineStr">
-        <is>
-          <t>FBS3[추정]</t>
+      <c r="D335" s="3" t="n"/>
+      <c r="E335" s="3" t="n"/>
+      <c r="F335" s="3" t="n"/>
+      <c r="G335" s="10" t="inlineStr">
+        <is>
+          <t>FBS3</t>
         </is>
       </c>
       <c r="H335" s="7" t="inlineStr">
@@ -18121,7 +18012,7 @@
       <c r="K335" s="7" t="inlineStr"/>
       <c r="L335" s="7" t="inlineStr"/>
       <c r="M335" s="7" t="inlineStr"/>
-      <c r="N335" s="4" t="inlineStr">
+      <c r="N335" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -18131,11 +18022,7 @@
           <t>wikipedia(W164 2005 생산 시작)</t>
         </is>
       </c>
-      <c r="P335" s="4" t="inlineStr">
-        <is>
-          <t>2005년식 W164 키 자료 없음 — 2006년식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P335" s="10" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
@@ -19843,10 +19730,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D369" s="3" t="inlineStr"/>
-      <c r="E369" s="3" t="inlineStr"/>
-      <c r="F369" s="3" t="inlineStr"/>
-      <c r="G369" s="4" t="inlineStr">
+      <c r="D369" s="3" t="n"/>
+      <c r="E369" s="3" t="n"/>
+      <c r="F369" s="3" t="n"/>
+      <c r="G369" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -19865,7 +19752,7 @@
       <c r="K369" s="7" t="inlineStr"/>
       <c r="L369" s="7" t="n"/>
       <c r="M369" s="7" t="inlineStr"/>
-      <c r="N369" s="4" t="inlineStr">
+      <c r="N369" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -19875,11 +19762,7 @@
           <t>partslinkent(2021-25 GLE53 AMG 순정 키), mbworld(2024 GLE53 key)</t>
         </is>
       </c>
-      <c r="P369" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P369" s="10" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
@@ -22083,7 +21966,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2016년식 FBS3·FBS4 자료 상충 — VIN 확인</t>
+          <t>2016년식 FBS3·FBS4 자료 상충(2016 G63 FBS4 실차 사례 있음) — VIN 확인</t>
         </is>
       </c>
     </row>
@@ -22561,10 +22444,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D422" s="3" t="inlineStr"/>
-      <c r="E422" s="3" t="inlineStr"/>
-      <c r="F422" s="3" t="inlineStr"/>
-      <c r="G422" s="4" t="inlineStr">
+      <c r="D422" s="3" t="n"/>
+      <c r="E422" s="3" t="n"/>
+      <c r="F422" s="3" t="n"/>
+      <c r="G422" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -22583,7 +22466,7 @@
       <c r="K422" s="7" t="inlineStr"/>
       <c r="L422" s="7" t="inlineStr"/>
       <c r="M422" s="7" t="inlineStr"/>
-      <c r="N422" s="4" t="inlineStr">
+      <c r="N422" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -22593,11 +22476,7 @@
           <t>autoevolution(2024.3 이후 페이스리프트)</t>
         </is>
       </c>
-      <c r="P422" s="4" t="inlineStr">
-        <is>
-          <t>2025년~ 페이스리프트(W465) 키 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P422" s="10" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="7" t="inlineStr">
@@ -22615,10 +22494,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D423" s="3" t="inlineStr"/>
-      <c r="E423" s="3" t="inlineStr"/>
-      <c r="F423" s="3" t="inlineStr"/>
-      <c r="G423" s="4" t="inlineStr">
+      <c r="D423" s="3" t="n"/>
+      <c r="E423" s="3" t="n"/>
+      <c r="F423" s="3" t="n"/>
+      <c r="G423" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -22637,7 +22516,7 @@
       <c r="K423" s="7" t="inlineStr"/>
       <c r="L423" s="7" t="inlineStr"/>
       <c r="M423" s="7" t="inlineStr"/>
-      <c r="N423" s="4" t="inlineStr">
+      <c r="N423" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -22647,11 +22526,7 @@
           <t>autoevolution(2024.3 이후 페이스리프트)</t>
         </is>
       </c>
-      <c r="P423" s="4" t="inlineStr">
-        <is>
-          <t>2025년~ 페이스리프트(W465) 키 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P423" s="10" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="7" t="inlineStr">
@@ -22853,7 +22728,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2016년식 FBS3·FBS4 자료 상충 — VIN 확인</t>
+          <t>2016년식 FBS3·FBS4 자료 상충(2016 G63 FBS4 실차 사례 있음) — VIN 확인</t>
         </is>
       </c>
     </row>
@@ -23281,10 +23156,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D436" s="3" t="inlineStr"/>
-      <c r="E436" s="3" t="inlineStr"/>
-      <c r="F436" s="3" t="inlineStr"/>
-      <c r="G436" s="4" t="inlineStr">
+      <c r="D436" s="3" t="n"/>
+      <c r="E436" s="3" t="n"/>
+      <c r="F436" s="3" t="n"/>
+      <c r="G436" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -23303,7 +23178,7 @@
       <c r="K436" s="7" t="inlineStr"/>
       <c r="L436" s="7" t="inlineStr"/>
       <c r="M436" s="7" t="inlineStr"/>
-      <c r="N436" s="4" t="inlineStr">
+      <c r="N436" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -23313,11 +23188,7 @@
           <t>autoevolution(2024.3 이후 페이스리프트)</t>
         </is>
       </c>
-      <c r="P436" s="4" t="inlineStr">
-        <is>
-          <t>2025년~ 페이스리프트(W465) 키 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P436" s="10" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="7" t="inlineStr">
@@ -23335,10 +23206,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D437" s="3" t="inlineStr"/>
-      <c r="E437" s="3" t="inlineStr"/>
-      <c r="F437" s="3" t="inlineStr"/>
-      <c r="G437" s="4" t="inlineStr">
+      <c r="D437" s="3" t="n"/>
+      <c r="E437" s="3" t="n"/>
+      <c r="F437" s="3" t="n"/>
+      <c r="G437" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -23357,7 +23228,7 @@
       <c r="K437" s="7" t="inlineStr"/>
       <c r="L437" s="7" t="inlineStr"/>
       <c r="M437" s="7" t="inlineStr"/>
-      <c r="N437" s="4" t="inlineStr">
+      <c r="N437" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -23367,11 +23238,7 @@
           <t>autoevolution(2024.3 이후 페이스리프트)</t>
         </is>
       </c>
-      <c r="P437" s="4" t="inlineStr">
-        <is>
-          <t>2025년~ 페이스리프트(W465) 키 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P437" s="10" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="7" t="inlineStr">
@@ -24649,10 +24516,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D462" s="3" t="inlineStr"/>
-      <c r="E462" s="3" t="inlineStr"/>
-      <c r="F462" s="3" t="inlineStr"/>
-      <c r="G462" s="4" t="inlineStr">
+      <c r="D462" s="3" t="n"/>
+      <c r="E462" s="3" t="n"/>
+      <c r="F462" s="3" t="n"/>
+      <c r="G462" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -24671,7 +24538,7 @@
       <c r="K462" s="7" t="inlineStr"/>
       <c r="L462" s="7" t="n"/>
       <c r="M462" s="7" t="inlineStr"/>
-      <c r="N462" s="4" t="inlineStr">
+      <c r="N462" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -24681,11 +24548,7 @@
           <t>amazon(2022-2025 S·E·C·GLC·SL 3버튼 키), mbusa(SL R232 2025 이모빌라이저)</t>
         </is>
       </c>
-      <c r="P462" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P462" s="10" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="7" t="inlineStr">
@@ -25189,10 +25052,10 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D472" s="3" t="inlineStr"/>
-      <c r="E472" s="3" t="inlineStr"/>
-      <c r="F472" s="3" t="inlineStr"/>
-      <c r="G472" s="4" t="inlineStr">
+      <c r="D472" s="3" t="n"/>
+      <c r="E472" s="3" t="n"/>
+      <c r="F472" s="3" t="n"/>
+      <c r="G472" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -25211,7 +25074,7 @@
       <c r="K472" s="7" t="inlineStr"/>
       <c r="L472" s="7" t="inlineStr"/>
       <c r="M472" s="7" t="inlineStr"/>
-      <c r="N472" s="4" t="inlineStr">
+      <c r="N472" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -25221,11 +25084,7 @@
           <t>pelicanparts(C192 2024-2025)</t>
         </is>
       </c>
-      <c r="P472" s="4" t="inlineStr">
-        <is>
-          <t>2024년~ 2세대(C192) 키 자료 없음 — 이전 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P472" s="10" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="7" t="inlineStr">
@@ -25243,10 +25102,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D473" s="3" t="inlineStr"/>
-      <c r="E473" s="3" t="inlineStr"/>
-      <c r="F473" s="3" t="inlineStr"/>
-      <c r="G473" s="4" t="inlineStr">
+      <c r="D473" s="3" t="n"/>
+      <c r="E473" s="3" t="n"/>
+      <c r="F473" s="3" t="n"/>
+      <c r="G473" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -25265,7 +25124,7 @@
       <c r="K473" s="7" t="inlineStr"/>
       <c r="L473" s="7" t="inlineStr"/>
       <c r="M473" s="7" t="inlineStr"/>
-      <c r="N473" s="4" t="inlineStr">
+      <c r="N473" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -25275,11 +25134,7 @@
           <t>pelicanparts(C192 2024-2025)</t>
         </is>
       </c>
-      <c r="P473" s="4" t="inlineStr">
-        <is>
-          <t>2024년~ 2세대(C192) 키 자료 없음 — 이전 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P473" s="10" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="7" t="inlineStr">
@@ -25297,10 +25152,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D474" s="3" t="inlineStr"/>
-      <c r="E474" s="3" t="inlineStr"/>
-      <c r="F474" s="3" t="inlineStr"/>
-      <c r="G474" s="4" t="inlineStr">
+      <c r="D474" s="3" t="n"/>
+      <c r="E474" s="3" t="n"/>
+      <c r="F474" s="3" t="n"/>
+      <c r="G474" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -25319,7 +25174,7 @@
       <c r="K474" s="7" t="inlineStr"/>
       <c r="L474" s="7" t="inlineStr"/>
       <c r="M474" s="7" t="inlineStr"/>
-      <c r="N474" s="4" t="inlineStr">
+      <c r="N474" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -25329,11 +25184,7 @@
           <t>pelicanparts(C192 2024-2025)</t>
         </is>
       </c>
-      <c r="P474" s="4" t="inlineStr">
-        <is>
-          <t>2024년~ 2세대(C192) 키 자료 없음 — 이전 세대 기준 추정</t>
-        </is>
-      </c>
+      <c r="P474" s="10" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="7" t="inlineStr">
@@ -25771,10 +25622,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D483" s="3" t="inlineStr"/>
-      <c r="E483" s="3" t="inlineStr"/>
-      <c r="F483" s="3" t="inlineStr"/>
-      <c r="G483" s="4" t="inlineStr">
+      <c r="D483" s="3" t="n"/>
+      <c r="E483" s="3" t="n"/>
+      <c r="F483" s="3" t="n"/>
+      <c r="G483" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -25797,7 +25648,7 @@
         </is>
       </c>
       <c r="M483" s="7" t="inlineStr"/>
-      <c r="N483" s="4" t="inlineStr">
+      <c r="N483" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -25807,11 +25658,7 @@
           <t>ebay.de(EQB X243 순정 A1779054606 2021-2025), mbworld(EQ 디지털 키 미지원)</t>
         </is>
       </c>
-      <c r="P483" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P483" s="10" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="7" t="inlineStr">
@@ -26045,10 +25892,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D488" s="3" t="inlineStr"/>
-      <c r="E488" s="3" t="inlineStr"/>
-      <c r="F488" s="3" t="inlineStr"/>
-      <c r="G488" s="4" t="inlineStr">
+      <c r="D488" s="3" t="n"/>
+      <c r="E488" s="3" t="n"/>
+      <c r="F488" s="3" t="n"/>
+      <c r="G488" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -26071,7 +25918,7 @@
         </is>
       </c>
       <c r="M488" s="7" t="inlineStr"/>
-      <c r="N488" s="4" t="inlineStr">
+      <c r="N488" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -26081,11 +25928,7 @@
           <t>ebay.de(EQB X243 순정 A1779054606 2021-2025), mbworld(EQ 디지털 키 미지원)</t>
         </is>
       </c>
-      <c r="P488" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P488" s="10" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="7" t="inlineStr">
@@ -26603,10 +26446,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D499" s="3" t="inlineStr"/>
-      <c r="E499" s="3" t="inlineStr"/>
-      <c r="F499" s="3" t="inlineStr"/>
-      <c r="G499" s="4" t="inlineStr">
+      <c r="D499" s="3" t="n"/>
+      <c r="E499" s="3" t="n"/>
+      <c r="F499" s="3" t="n"/>
+      <c r="G499" s="10" t="inlineStr">
         <is>
           <t>FBS4</t>
         </is>
@@ -26625,17 +26468,13 @@
       <c r="K499" s="7" t="inlineStr"/>
       <c r="L499" s="7" t="n"/>
       <c r="M499" s="7" t="inlineStr"/>
-      <c r="N499" s="4" t="inlineStr">
+      <c r="N499" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
       </c>
       <c r="O499" s="7" t="inlineStr"/>
-      <c r="P499" s="4" t="inlineStr">
-        <is>
-          <t>해당 연식 검색 자료 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P499" s="10" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="7" t="inlineStr">
@@ -27056,184 +26895,184 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr"/>
+      <c r="A2" s="9" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같고, 칩코드 뒤에 '키종류'를 추가했습니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(G클래스 구형은 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 벤츠는 EIS(EZS)에 꽂는 크롬키·키리스고 키 모두 '스마트키'로 적었고, 폴딩키·카드키는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433MHz)만 적었습니다. 미국(315MHz) 사양 키(FCC IYZ3312·NBGDM3 등)는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2019(단종)' 형식입니다. 원본 목록 연식을 그대로 따랐습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">- 벤츠 키는 ID46 같은 일반 트랜스폰더가 아니라 NEC 프로세서 키(FBS3/FBS4)라서 'XT27A/A66·XT27B·XT57B 호환' 칸은 비어 있습니다(기아 파일 규칙상 해당 칩 없음). </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>- 이모빌라이저는 EIS(EZS, 전자식 점화 스위치 모듈)입니다. FBS3/FBS4 세대는 칩코드 칸에 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>- 키블레이드(키웨이)는 비상키 블레이드 HU64입니다(1997~2014 인서트 및 2019+ FBS4 비상키 모두 HU64 표기). 키블레이드 부품번호는 찾지 못해 비웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr"/>
+      <c r="A14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값, 또는 해당 연식 검색 자료가 없어 이전 연식 기준으로 채운 값 — 실물 키/VIN(SA코드 803/804 = FBS4)으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>- 전환 연식(FBS3→FBS4)은 색 없이 칩코드·이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: FBS3[2013.4 이전 생산], FBS4[2013.4 이후 생산]).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr"/>
+      <c r="A18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 검색했고 연식별 검색 기록은 research/benz/yearly.md에 있습니다. 같은 세대 안에서도 FBS3→FBS4 전환, 페이스리프트 후 신형 키 디자인, 키리스고 옵션 여부가 달라집니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>- 신형 키 디자인: E클래스 W213 2017~, S클래스 2018 페이스리프트~, G클래스 2019~, A·C·CLA·CLS·GLB·GLC·GLS 2020~(Gen3), GLE W167 2019~(티어드롭), 2021~ W223·W206·W214·X254·EQS/EQE는 MS5 계열 신형 키. 구형 키와 호환 안 됨.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>- 확인된 국내 사양(433/434MHz) 순정 품번: W205 A2059053609(3버튼)·A2059050000/A2059050600(2버튼), W222·C217·X222 A2229059610, W177 A1779057902, EQA·EQB A1779054606, FBS4 공용 보드 IYZDC12B.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>- FBS4 적용 시점: W212 2013.4~, 166(ML·GL)·207(E쿠페/카브리올레)·V212 2013.7~, 218(CLS) 2014.9~, 117(CLA)·156(GLA) 2014.11~, 172(SLK) 2015.4~, 205·217·222·231은 처음부터 FBS4. A클래스 W176은 2014년부터 FBS4.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>- FBS3 키는 로컬 장비(NEC/BGA 등)로 키 제작이 가능하지만, FBS4는 독일 벤츠 서버 인증이 필요해 사실상 딜러(또는 XENTRY 계정 보유 업체) 작업입니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>- 2021년 이후 신형(W206·W223·W214·X254·EQS/EQE 등)도 FBS4 딜러 전용으로 분류됩니다. 비상키는 Gen4 인서트(HU64).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>- FBS3/FBS4 키 구분: 키 기판 번호 문자열에 'K'가 앞에 있으면 FBS3 풀 스마트키, 중간에 있으면 FBS4 풀 스마트키. FBS4 기판에는 오른쪽에 트랜지스터가 있고 칩이 더 작습니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>- 순정 FBS4 스마트키(433MHz, 3버튼) IYZDC12B는 2014-2023년식 적용 표기, W222 S클래스 FBS4 키리스고 키 A2229059610(433MHz).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>- G클래스(W463) 구형: 2000~2001년식 키 자료 상충, 2002~2005년식 IR 스마트키·트랜스폰더 막대키 병존, 2006년식 검정 키, 2007년형부터 크롬 키, 2016년식 FBS3/FBS4 자료 상충.</t>
         </is>

--- a/벤츠_models.xlsx
+++ b/벤츠_models.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -660,9 +663,9 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FBS3</t>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>FBS3[2014.11 이전 생산]</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -679,7 +682,7 @@
       <c r="K3" s="7" t="n"/>
       <c r="L3" s="7" t="n"/>
       <c r="M3" s="7" t="n"/>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -689,11 +692,7 @@
           <t>amazon EASYGUARD(2014+ FBS4 W176), dallaslocksmithspro(2014 A180 FBS3 범주)</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>2014년식 FBS3·FBS4 전환 월 자료 없음(미국형은 2014부터 FBS4) — VIN(SA코드 803/804) 확인</t>
-        </is>
-      </c>
+      <c r="P3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -714,9 +713,9 @@
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>FBS4</t>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FBS4[2014.11 이후 생산]</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -733,7 +732,7 @@
       <c r="K4" s="7" t="n"/>
       <c r="L4" s="7" t="n"/>
       <c r="M4" s="7" t="n"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -743,11 +742,7 @@
           <t>amazon EASYGUARD(2014+ FBS4 W176), dallaslocksmithspro(2014 A180 FBS3 범주)</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
-        <is>
-          <t>2014년식 FBS3·FBS4 전환 월 자료 없음(미국형은 2014부터 FBS4) — VIN(SA코드 803/804) 확인</t>
-        </is>
-      </c>
+      <c r="P4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1408,9 +1403,9 @@
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>FBS3</t>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>FBS3[2014.11 이전 생산]</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
@@ -1427,7 +1422,7 @@
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
       <c r="M17" s="7" t="n"/>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -1437,11 +1432,7 @@
           <t>diag.net·doornkey(2014 A45 FBS3 가능), amazon EASYGUARD(2014+ FBS4 W176)</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
-        <is>
-          <t>2014년식 FBS3·FBS4 전환 월 자료 없음(미국형은 2014부터 FBS4) — VIN(SA코드 803/804) 확인</t>
-        </is>
-      </c>
+      <c r="P17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1462,9 +1453,9 @@
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>FBS4</t>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>FBS4[2014.11 이후 생산]</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -1481,7 +1472,7 @@
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
       <c r="M18" s="7" t="n"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -1491,11 +1482,7 @@
           <t>diag.net·doornkey(2014 A45 FBS3 가능), amazon EASYGUARD(2014+ FBS4 W176)</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
-        <is>
-          <t>2014년식 FBS3·FBS4 전환 월 자료 없음(미국형은 2014부터 FBS4) — VIN(SA코드 803/804) 확인</t>
-        </is>
-      </c>
+      <c r="P18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -2264,9 +2251,9 @@
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>FBS3</t>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>FBS3[2014.11 이전 생산]</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -2283,7 +2270,7 @@
       <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n"/>
       <c r="M33" s="7" t="n"/>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -2293,11 +2280,7 @@
           <t>amazon EASYGUARD(2014+ FBS4 W246), abkeys(W246 EZS FBS4 2469057503)</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>W246 FBS4 EZS는 2015년 이후 표기 — 2014년식 FBS3·FBS4 혼재 가능, VIN 확인</t>
-        </is>
-      </c>
+      <c r="P33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -2318,9 +2301,9 @@
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>FBS4</t>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>FBS4[2014.11 이후 생산]</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -2337,7 +2320,7 @@
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
       <c r="M34" s="7" t="n"/>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -2347,11 +2330,7 @@
           <t>amazon EASYGUARD(2014+ FBS4 W246), abkeys(W246 EZS FBS4 2469057503)</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>W246 FBS4 EZS는 2015년 이후 표기 — 2014년식 FBS3·FBS4 혼재 가능, VIN 확인</t>
-        </is>
-      </c>
+      <c r="P34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -21897,7 +21876,7 @@
       <c r="M411" s="7" t="inlineStr"/>
       <c r="N411" s="4" t="inlineStr">
         <is>
-          <t>EIS, DAS</t>
+          <t>DAS 2a, DAS 2b</t>
         </is>
       </c>
       <c r="O411" s="7" t="inlineStr">
@@ -21907,7 +21886,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>W463 초기형 키 자료 상충(칩 없는 IR 키 의견 vs DAS3/FBS3) — 실물 확인 필요</t>
+          <t>DAS 2a·2b(1997~2001, 키 트랜스폰더) 확인 — 키 트랜스폰더 칩 형식 자료 없음(같은 DAS2 W163은 PCF7930·PCF7931·PCF7935)</t>
         </is>
       </c>
     </row>
@@ -21951,7 +21930,7 @@
       <c r="M412" s="7" t="inlineStr"/>
       <c r="N412" s="4" t="inlineStr">
         <is>
-          <t>EIS, DAS</t>
+          <t>DAS 2a, DAS 2b</t>
         </is>
       </c>
       <c r="O412" s="7" t="inlineStr">
@@ -21961,7 +21940,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>W463 초기형 키 자료 상충(칩 없는 IR 키 의견 vs DAS3/FBS3) — 실물 확인 필요</t>
+          <t>DAS 2a·2b(1997~2001, 키 트랜스폰더) 확인 — 키 트랜스폰더 칩 형식 자료 없음(같은 DAS2 W163은 PCF7930·PCF7931·PCF7935)</t>
         </is>
       </c>
     </row>
@@ -21981,17 +21960,17 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="D413" s="3" t="inlineStr"/>
-      <c r="E413" s="3" t="inlineStr"/>
-      <c r="F413" s="3" t="inlineStr"/>
-      <c r="G413" s="4" t="inlineStr">
-        <is>
-          <t>FBS3[적외선 키], FBS3[트랜스폰더 키]</t>
+      <c r="D413" s="3" t="n"/>
+      <c r="E413" s="3" t="n"/>
+      <c r="F413" s="3" t="n"/>
+      <c r="G413" s="10" t="inlineStr">
+        <is>
+          <t>FBS3</t>
         </is>
       </c>
       <c r="H413" s="7" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I413" s="7" t="inlineStr"/>
@@ -22003,7 +21982,7 @@
       <c r="K413" s="7" t="inlineStr"/>
       <c r="L413" s="7" t="n"/>
       <c r="M413" s="7" t="inlineStr"/>
-      <c r="N413" s="4" t="inlineStr">
+      <c r="N413" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -22013,11 +21992,7 @@
           <t>keylessentryremotefob(2002-2005 G500 트랜스폰더 키), auto-key.no(G 2002-2009 IR 키), fixautosmart(G500 2002-2014 EIS)</t>
         </is>
       </c>
-      <c r="P413" s="4" t="inlineStr">
-        <is>
-          <t>IR 스마트키와 트랜스폰더 막대키 자료 병존 — 차량별 확인</t>
-        </is>
-      </c>
+      <c r="P413" s="10" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="7" t="inlineStr">
@@ -22035,17 +22010,17 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="D414" s="3" t="inlineStr"/>
-      <c r="E414" s="3" t="inlineStr"/>
-      <c r="F414" s="3" t="inlineStr"/>
-      <c r="G414" s="4" t="inlineStr">
-        <is>
-          <t>FBS3[적외선 키], FBS3[트랜스폰더 키]</t>
+      <c r="D414" s="3" t="n"/>
+      <c r="E414" s="3" t="n"/>
+      <c r="F414" s="3" t="n"/>
+      <c r="G414" s="10" t="inlineStr">
+        <is>
+          <t>FBS3</t>
         </is>
       </c>
       <c r="H414" s="7" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I414" s="7" t="inlineStr"/>
@@ -22057,7 +22032,7 @@
       <c r="K414" s="7" t="inlineStr"/>
       <c r="L414" s="7" t="n"/>
       <c r="M414" s="7" t="inlineStr"/>
-      <c r="N414" s="4" t="inlineStr">
+      <c r="N414" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -22067,11 +22042,7 @@
           <t>keylessentryremotefob(2002-2005 G500 트랜스폰더 키), auto-key.no(G 2002-2009 IR 키), fixautosmart(G500 2002-2014 EIS)</t>
         </is>
       </c>
-      <c r="P414" s="4" t="inlineStr">
-        <is>
-          <t>IR 스마트키와 트랜스폰더 막대키 자료 병존 — 차량별 확인</t>
-        </is>
-      </c>
+      <c r="P414" s="10" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="7" t="inlineStr">
@@ -22089,17 +22060,17 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="D415" s="3" t="inlineStr"/>
-      <c r="E415" s="3" t="inlineStr"/>
-      <c r="F415" s="3" t="inlineStr"/>
-      <c r="G415" s="4" t="inlineStr">
-        <is>
-          <t>FBS3[적외선 키], FBS3[트랜스폰더 키]</t>
+      <c r="D415" s="3" t="n"/>
+      <c r="E415" s="3" t="n"/>
+      <c r="F415" s="3" t="n"/>
+      <c r="G415" s="10" t="inlineStr">
+        <is>
+          <t>FBS3</t>
         </is>
       </c>
       <c r="H415" s="7" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I415" s="7" t="inlineStr"/>
@@ -22111,7 +22082,7 @@
       <c r="K415" s="7" t="inlineStr"/>
       <c r="L415" s="7" t="n"/>
       <c r="M415" s="7" t="inlineStr"/>
-      <c r="N415" s="4" t="inlineStr">
+      <c r="N415" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -22121,11 +22092,7 @@
           <t>keylessentryremotefob(2002-2005 G500 트랜스폰더 키), auto-key.no(G 2002-2009 IR 키), fixautosmart(G500 2002-2014 EIS)</t>
         </is>
       </c>
-      <c r="P415" s="4" t="inlineStr">
-        <is>
-          <t>IR 스마트키와 트랜스폰더 막대키 자료 병존 — 차량별 확인</t>
-        </is>
-      </c>
+      <c r="P415" s="10" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="7" t="inlineStr">
@@ -22143,17 +22110,17 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="D416" s="3" t="inlineStr"/>
-      <c r="E416" s="3" t="inlineStr"/>
-      <c r="F416" s="3" t="inlineStr"/>
-      <c r="G416" s="4" t="inlineStr">
-        <is>
-          <t>FBS3[적외선 키], FBS3[트랜스폰더 키]</t>
+      <c r="D416" s="3" t="n"/>
+      <c r="E416" s="3" t="n"/>
+      <c r="F416" s="3" t="n"/>
+      <c r="G416" s="10" t="inlineStr">
+        <is>
+          <t>FBS3</t>
         </is>
       </c>
       <c r="H416" s="7" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I416" s="7" t="inlineStr"/>
@@ -22165,7 +22132,7 @@
       <c r="K416" s="7" t="inlineStr"/>
       <c r="L416" s="7" t="n"/>
       <c r="M416" s="7" t="inlineStr"/>
-      <c r="N416" s="4" t="inlineStr">
+      <c r="N416" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
@@ -22175,11 +22142,7 @@
           <t>keylessentryremotefob(2002-2005 G500 트랜스폰더 키), auto-key.no(G 2002-2009 IR 키), fixautosmart(G500 2002-2014 EIS)</t>
         </is>
       </c>
-      <c r="P416" s="4" t="inlineStr">
-        <is>
-          <t>IR 스마트키와 트랜스폰더 막대키 자료 병존 — 차량별 확인</t>
-        </is>
-      </c>
+      <c r="P416" s="10" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="7" t="inlineStr">
@@ -27811,328 +27774,352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr"/>
+      <c r="A2" s="12" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같고, 칩코드 뒤에 '키종류'를 추가했습니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(G클래스 구형은 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 벤츠는 EIS(EZS)에 꽂는 크롬키·키리스고 키 모두 '스마트키'로 적었고, 폴딩키·카드키는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433MHz)만 적었습니다. 미국(315MHz) 사양 키(FCC IYZ3312·NBGDM3 등)는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2019(단종)' 형식입니다. 원본 목록 연식을 그대로 따랐습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">- 벤츠 키는 ID46 같은 일반 트랜스폰더가 아니라 NEC 프로세서 키(FBS3/FBS4)라서 'XT27A/A66·XT27B·XT57B 호환' 칸은 비어 있습니다(기아 파일 규칙상 해당 칩 없음). </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>- 이모빌라이저는 EIS(EZS, 전자식 점화 스위치 모듈)입니다. FBS3/FBS4 세대는 칩코드 칸에 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>- 키블레이드(키웨이)는 비상키 블레이드 HU64입니다(1997~2014 인서트 및 2019+ FBS4 비상키 모두 HU64 표기). 키블레이드 부품번호는 찾지 못해 비웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr"/>
+      <c r="A14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값, 또는 해당 연식 검색 자료가 없어 이전 연식 기준으로 채운 값 — 실물 키/VIN(SA코드 803/804 = FBS4)으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>- 전환 연식(FBS3→FBS4)은 색 없이 칩코드·이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: FBS3[2013.4 이전 생산], FBS4[2013.4 이후 생산]).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 검색했고 연식별 검색 기록은 research/benz/yearly.md에 있습니다. 같은 세대 안에서도 FBS3→FBS4 전환, 페이스리프트 후 신형 키 디자인, 키리스고 옵션 여부가 달라집니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>- 신형 키 디자인: E클래스 W213 2017~, S클래스 2018 페이스리프트~, G클래스 2019~, A·C·CLA·CLS·GLB·GLC·GLS 2020~(Gen3), GLE W167 2019~(티어드롭), 2021~ W223·W206·W214·X254·EQS/EQE는 MS5 계열 신형 키. 구형 키와 호환 안 됨.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>- 확인된 국내 사양(433/434MHz) 순정 품번: W205 A2059053609(3버튼)·A2059050000/A2059050600(2버튼), W222·C217·X222 A2229059610, W177 A1779057902, EQA·EQB A1779054606, FBS4 공용 보드 IYZDC12B.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>- FBS4 적용 시점: W212 2013.4~, 166(ML·GL)·207(E쿠페/카브리올레)·V212 2013.7~, 218(CLS) 2014.9~, 117(CLA)·156(GLA) 2014.11~, 172(SLK) 2015.4~, 205·217·222·231은 처음부터 FBS4. A클래스 W176은 2014년부터 FBS4.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>- FBS3 키는 로컬 장비(NEC/BGA 등)로 키 제작이 가능하지만, FBS4는 독일 벤츠 서버 인증이 필요해 사실상 딜러(또는 XENTRY 계정 보유 업체) 작업입니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>- 2021년 이후 신형(W206·W223·W214·X254·EQS/EQE 등)도 FBS4 딜러 전용으로 분류됩니다. 비상키는 Gen4 인서트(HU64).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>- FBS3/FBS4 키 구분: 키 기판 번호 문자열에 'K'가 앞에 있으면 FBS3 풀 스마트키, 중간에 있으면 FBS4 풀 스마트키. FBS4 기판에는 오른쪽에 트랜지스터가 있고 칩이 더 작습니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>- 순정 FBS4 스마트키(433MHz, 3버튼) IYZDC12B는 2014-2023년식 적용 표기, W222 S클래스 FBS4 키리스고 키 A2229059610(433MHz).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>- G클래스(W463) 구형: 2000~2001년식 키 자료 상충, 2002~2005년식 IR 스마트키·트랜스폰더 막대키 병존, 2006년식 검정 키, 2007년형부터 크롬 키, 2016년식 FBS3/FBS4 자료 상충.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n"/>
+      <c r="A29" s="12" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="n"/>
+      <c r="A37" s="12" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="n"/>
+      <c r="A46" s="12" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>- W246 FBS4는 2014.11 생산부터(EASYGUARD·abkeys W246 FBS4 EZS 2469057503) — 같은 MFA 플랫폼 W176·A45·CLA·GLA도 2014.11 전환으로 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>- G클래스 W463 2002~: EIS(EZS) + 적외선 키(FBS3)로 바뀜(fixautosmart "G500 2002-2014 W463 EIS", CGDI MB G클래스 2003~ 적외선 모드) — 트랜스폰더 막대키는 2001년까지 DAS 차량</t>
         </is>
       </c>
     </row>

--- a/벤츠_models.xlsx
+++ b/벤츠_models.xlsx
@@ -28005,7 +28005,7 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>

--- a/벤츠_models.xlsx
+++ b/벤츠_models.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -3862,7 +3865,11 @@
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr"/>
-      <c r="L64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[2버튼, 해외 공용 품번], A2049055702[3버튼, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="7" t="inlineStr">
         <is>
@@ -3912,7 +3919,11 @@
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr"/>
-      <c r="L65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[2버튼, 해외 공용 품번], A2049055702[3버튼, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M65" s="7" t="inlineStr"/>
       <c r="N65" s="7" t="inlineStr">
         <is>
@@ -3962,7 +3973,11 @@
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr"/>
-      <c r="L66" s="7" t="inlineStr"/>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[2버튼, 해외 공용 품번], A2049055702[3버튼, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M66" s="7" t="inlineStr"/>
       <c r="N66" s="7" t="inlineStr">
         <is>
@@ -4012,7 +4027,11 @@
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr"/>
-      <c r="L67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[2버튼, 해외 공용 품번], A2049055702[3버튼, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M67" s="7" t="inlineStr"/>
       <c r="N67" s="7" t="inlineStr">
         <is>
@@ -4062,7 +4081,11 @@
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr"/>
-      <c r="L68" s="7" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[2버튼, 해외 공용 품번], A2049055702[3버튼, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M68" s="7" t="inlineStr"/>
       <c r="N68" s="7" t="inlineStr">
         <is>
@@ -4112,7 +4135,11 @@
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr"/>
-      <c r="L69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[2버튼, 해외 공용 품번], A2049055702[3버튼, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M69" s="7" t="inlineStr"/>
       <c r="N69" s="7" t="inlineStr">
         <is>
@@ -4162,7 +4189,11 @@
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr"/>
-      <c r="L70" s="7" t="inlineStr"/>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[2버튼, 해외 공용 품번], A2049055702[3버튼, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M70" s="7" t="inlineStr"/>
       <c r="N70" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4243,11 @@
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr"/>
-      <c r="L71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[2버튼, 해외 공용 품번], A2049055702[3버튼, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="7" t="inlineStr">
         <is>
@@ -4694,7 +4729,11 @@
         </is>
       </c>
       <c r="K80" s="7" t="inlineStr"/>
-      <c r="L80" s="7" t="n"/>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>A2239058707[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M80" s="7" t="inlineStr"/>
       <c r="N80" s="7" t="inlineStr">
         <is>
@@ -4744,7 +4783,11 @@
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr"/>
-      <c r="L81" s="7" t="n"/>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>A2239058707[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M81" s="7" t="inlineStr"/>
       <c r="N81" s="7" t="inlineStr">
         <is>
@@ -4794,7 +4837,11 @@
         </is>
       </c>
       <c r="K82" s="7" t="inlineStr"/>
-      <c r="L82" s="7" t="n"/>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>A2239058707[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="7" t="inlineStr">
         <is>
@@ -4844,7 +4891,11 @@
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr"/>
-      <c r="L83" s="7" t="n"/>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>A2239058707[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M83" s="7" t="inlineStr"/>
       <c r="N83" s="7" t="inlineStr">
         <is>
@@ -4894,7 +4945,11 @@
         </is>
       </c>
       <c r="K84" s="7" t="inlineStr"/>
-      <c r="L84" s="7" t="n"/>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>A2239058707[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M84" s="7" t="inlineStr"/>
       <c r="N84" s="7" t="inlineStr">
         <is>
@@ -6186,7 +6241,11 @@
         </is>
       </c>
       <c r="K108" s="7" t="inlineStr"/>
-      <c r="L108" s="7" t="n"/>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>A2239058707[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M108" s="7" t="inlineStr"/>
       <c r="N108" s="7" t="inlineStr">
         <is>
@@ -6236,7 +6295,11 @@
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr"/>
-      <c r="L109" s="7" t="n"/>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>A2239058707[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M109" s="7" t="inlineStr"/>
       <c r="N109" s="7" t="inlineStr">
         <is>
@@ -6286,7 +6349,11 @@
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr"/>
-      <c r="L110" s="7" t="n"/>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>A2239058707[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M110" s="7" t="inlineStr"/>
       <c r="N110" s="10" t="inlineStr">
         <is>
@@ -7350,7 +7417,7 @@
       <c r="K131" s="7" t="inlineStr"/>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139059209[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M131" s="7" t="inlineStr"/>
@@ -7404,7 +7471,7 @@
       <c r="K132" s="7" t="inlineStr"/>
       <c r="L132" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139059209[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M132" s="7" t="inlineStr"/>
@@ -7458,7 +7525,7 @@
       <c r="K133" s="7" t="inlineStr"/>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139059209[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M133" s="7" t="inlineStr"/>
@@ -7512,7 +7579,7 @@
       <c r="K134" s="7" t="inlineStr"/>
       <c r="L134" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139059209[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M134" s="7" t="inlineStr"/>
@@ -7566,7 +7633,7 @@
       <c r="K135" s="7" t="inlineStr"/>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139059209[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M135" s="7" t="inlineStr"/>
@@ -7620,7 +7687,7 @@
       <c r="K136" s="7" t="inlineStr"/>
       <c r="L136" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139059209[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M136" s="7" t="inlineStr"/>
@@ -7674,7 +7741,7 @@
       <c r="K137" s="7" t="inlineStr"/>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139059209[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M137" s="7" t="inlineStr"/>
@@ -7728,7 +7795,7 @@
       <c r="K138" s="7" t="inlineStr"/>
       <c r="L138" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139059209[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M138" s="7" t="inlineStr"/>
@@ -7780,7 +7847,11 @@
         </is>
       </c>
       <c r="K139" s="7" t="inlineStr"/>
-      <c r="L139" s="7" t="n"/>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>A2139059209[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M139" s="7" t="inlineStr"/>
       <c r="N139" s="10" t="inlineStr">
         <is>
@@ -9670,7 +9741,7 @@
       <c r="K175" s="7" t="inlineStr"/>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139056509[AMG, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M175" s="7" t="inlineStr"/>
@@ -9724,7 +9795,7 @@
       <c r="K176" s="7" t="inlineStr"/>
       <c r="L176" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139056509[AMG, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M176" s="7" t="inlineStr"/>
@@ -9778,7 +9849,7 @@
       <c r="K177" s="7" t="inlineStr"/>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139056509[AMG, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M177" s="7" t="inlineStr"/>
@@ -9832,7 +9903,7 @@
       <c r="K178" s="7" t="inlineStr"/>
       <c r="L178" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139056509[AMG, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M178" s="7" t="inlineStr"/>
@@ -9886,7 +9957,7 @@
       <c r="K179" s="7" t="inlineStr"/>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139056509[AMG, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M179" s="7" t="inlineStr"/>
@@ -9940,7 +10011,7 @@
       <c r="K180" s="7" t="inlineStr"/>
       <c r="L180" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139056509[AMG, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M180" s="7" t="inlineStr"/>
@@ -9994,7 +10065,7 @@
       <c r="K181" s="7" t="inlineStr"/>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2139056509[AMG, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M181" s="7" t="inlineStr"/>
@@ -12700,7 +12771,11 @@
         </is>
       </c>
       <c r="K233" s="7" t="inlineStr"/>
-      <c r="L233" s="7" t="n"/>
+      <c r="L233" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M233" s="7" t="inlineStr"/>
       <c r="N233" s="7" t="inlineStr">
         <is>
@@ -12750,7 +12825,11 @@
         </is>
       </c>
       <c r="K234" s="7" t="inlineStr"/>
-      <c r="L234" s="7" t="n"/>
+      <c r="L234" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M234" s="7" t="inlineStr"/>
       <c r="N234" s="7" t="inlineStr">
         <is>
@@ -12800,7 +12879,11 @@
         </is>
       </c>
       <c r="K235" s="7" t="inlineStr"/>
-      <c r="L235" s="7" t="n"/>
+      <c r="L235" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M235" s="7" t="inlineStr"/>
       <c r="N235" s="7" t="inlineStr">
         <is>
@@ -12850,7 +12933,11 @@
         </is>
       </c>
       <c r="K236" s="7" t="inlineStr"/>
-      <c r="L236" s="7" t="n"/>
+      <c r="L236" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M236" s="7" t="inlineStr"/>
       <c r="N236" s="7" t="inlineStr">
         <is>
@@ -12900,7 +12987,11 @@
         </is>
       </c>
       <c r="K237" s="7" t="inlineStr"/>
-      <c r="L237" s="7" t="n"/>
+      <c r="L237" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M237" s="7" t="inlineStr"/>
       <c r="N237" s="7" t="inlineStr">
         <is>
@@ -12950,7 +13041,11 @@
         </is>
       </c>
       <c r="K238" s="7" t="inlineStr"/>
-      <c r="L238" s="7" t="n"/>
+      <c r="L238" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M238" s="7" t="inlineStr"/>
       <c r="N238" s="10" t="inlineStr">
         <is>
@@ -14754,7 +14849,11 @@
         </is>
       </c>
       <c r="K272" s="7" t="inlineStr"/>
-      <c r="L272" s="7" t="n"/>
+      <c r="L272" s="7" t="inlineStr">
+        <is>
+          <t>A2239054408[AMG, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M272" s="7" t="inlineStr"/>
       <c r="N272" s="10" t="inlineStr">
         <is>
@@ -14804,7 +14903,11 @@
         </is>
       </c>
       <c r="K273" s="7" t="inlineStr"/>
-      <c r="L273" s="7" t="n"/>
+      <c r="L273" s="7" t="inlineStr">
+        <is>
+          <t>A2239054408[AMG, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M273" s="7" t="inlineStr"/>
       <c r="N273" s="7" t="inlineStr">
         <is>
@@ -14854,7 +14957,11 @@
         </is>
       </c>
       <c r="K274" s="7" t="inlineStr"/>
-      <c r="L274" s="7" t="n"/>
+      <c r="L274" s="7" t="inlineStr">
+        <is>
+          <t>A2239054408[AMG, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M274" s="7" t="inlineStr"/>
       <c r="N274" s="7" t="inlineStr">
         <is>
@@ -14904,7 +15011,11 @@
         </is>
       </c>
       <c r="K275" s="7" t="inlineStr"/>
-      <c r="L275" s="7" t="n"/>
+      <c r="L275" s="7" t="inlineStr">
+        <is>
+          <t>A2239054408[AMG, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M275" s="7" t="inlineStr"/>
       <c r="N275" s="7" t="inlineStr">
         <is>
@@ -14954,7 +15065,11 @@
         </is>
       </c>
       <c r="K276" s="7" t="inlineStr"/>
-      <c r="L276" s="7" t="n"/>
+      <c r="L276" s="7" t="inlineStr">
+        <is>
+          <t>A2239054408[AMG, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M276" s="7" t="inlineStr"/>
       <c r="N276" s="10" t="inlineStr">
         <is>
@@ -19528,7 +19643,11 @@
         </is>
       </c>
       <c r="K365" s="7" t="inlineStr"/>
-      <c r="L365" s="7" t="n"/>
+      <c r="L365" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M365" s="7" t="inlineStr"/>
       <c r="N365" s="7" t="inlineStr">
         <is>
@@ -19578,7 +19697,11 @@
         </is>
       </c>
       <c r="K366" s="7" t="inlineStr"/>
-      <c r="L366" s="7" t="n"/>
+      <c r="L366" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M366" s="7" t="inlineStr"/>
       <c r="N366" s="7" t="inlineStr">
         <is>
@@ -19628,7 +19751,11 @@
         </is>
       </c>
       <c r="K367" s="7" t="inlineStr"/>
-      <c r="L367" s="7" t="n"/>
+      <c r="L367" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M367" s="7" t="inlineStr"/>
       <c r="N367" s="7" t="inlineStr">
         <is>
@@ -19678,7 +19805,11 @@
         </is>
       </c>
       <c r="K368" s="7" t="inlineStr"/>
-      <c r="L368" s="7" t="n"/>
+      <c r="L368" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M368" s="7" t="inlineStr"/>
       <c r="N368" s="7" t="inlineStr">
         <is>
@@ -19728,7 +19859,11 @@
         </is>
       </c>
       <c r="K369" s="7" t="inlineStr"/>
-      <c r="L369" s="7" t="n"/>
+      <c r="L369" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M369" s="7" t="inlineStr"/>
       <c r="N369" s="7" t="inlineStr">
         <is>
@@ -19778,7 +19913,11 @@
         </is>
       </c>
       <c r="K370" s="7" t="inlineStr"/>
-      <c r="L370" s="7" t="n"/>
+      <c r="L370" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M370" s="7" t="inlineStr"/>
       <c r="N370" s="7" t="inlineStr">
         <is>
@@ -19828,7 +19967,11 @@
         </is>
       </c>
       <c r="K371" s="7" t="inlineStr"/>
-      <c r="L371" s="7" t="n"/>
+      <c r="L371" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M371" s="7" t="inlineStr"/>
       <c r="N371" s="7" t="inlineStr">
         <is>
@@ -19878,7 +20021,11 @@
         </is>
       </c>
       <c r="K372" s="7" t="inlineStr"/>
-      <c r="L372" s="7" t="n"/>
+      <c r="L372" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M372" s="7" t="inlineStr"/>
       <c r="N372" s="7" t="inlineStr">
         <is>
@@ -20144,7 +20291,11 @@
         </is>
       </c>
       <c r="K377" s="7" t="inlineStr"/>
-      <c r="L377" s="7" t="n"/>
+      <c r="L377" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M377" s="7" t="inlineStr"/>
       <c r="N377" s="7" t="inlineStr">
         <is>
@@ -20194,7 +20345,11 @@
         </is>
       </c>
       <c r="K378" s="7" t="inlineStr"/>
-      <c r="L378" s="7" t="n"/>
+      <c r="L378" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M378" s="7" t="inlineStr"/>
       <c r="N378" s="7" t="inlineStr">
         <is>
@@ -20244,7 +20399,11 @@
         </is>
       </c>
       <c r="K379" s="7" t="inlineStr"/>
-      <c r="L379" s="7" t="n"/>
+      <c r="L379" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M379" s="7" t="inlineStr"/>
       <c r="N379" s="7" t="inlineStr">
         <is>
@@ -20294,7 +20453,11 @@
         </is>
       </c>
       <c r="K380" s="7" t="inlineStr"/>
-      <c r="L380" s="7" t="n"/>
+      <c r="L380" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M380" s="7" t="inlineStr"/>
       <c r="N380" s="7" t="inlineStr">
         <is>
@@ -20344,7 +20507,11 @@
         </is>
       </c>
       <c r="K381" s="7" t="inlineStr"/>
-      <c r="L381" s="7" t="n"/>
+      <c r="L381" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M381" s="7" t="inlineStr"/>
       <c r="N381" s="7" t="inlineStr">
         <is>
@@ -20394,7 +20561,11 @@
         </is>
       </c>
       <c r="K382" s="7" t="inlineStr"/>
-      <c r="L382" s="7" t="n"/>
+      <c r="L382" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M382" s="7" t="inlineStr"/>
       <c r="N382" s="7" t="inlineStr">
         <is>
@@ -20444,7 +20615,11 @@
         </is>
       </c>
       <c r="K383" s="7" t="inlineStr"/>
-      <c r="L383" s="7" t="n"/>
+      <c r="L383" s="7" t="inlineStr">
+        <is>
+          <t>A1679054203[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M383" s="7" t="inlineStr"/>
       <c r="N383" s="10" t="inlineStr">
         <is>
@@ -27774,7 +27949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -28123,6 +28298,13 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>- 벤츠 순정 부품번호(공란 행 보완, auto-keys.eu OEM 키 433/434MHz): W204 A2049051704(2버튼, FBS3)·A2049055702(3버튼), W213 A2139059209·A2139056509(AMG), W206 A2239058707, W223 A2239057507·A2239054408(AMG), W167 A1679054203 — 315MHz 번호(A1679054503 등) 제외, 한국 사양 번호 미확인이라 [해외 공용 품번]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/벤츠_models.xlsx
+++ b/벤츠_models.xlsx
@@ -27956,343 +27956,343 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr"/>
+      <c r="A2" s="13" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같고, 칩코드 뒤에 '키종류'를 추가했습니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(G클래스 구형은 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 벤츠는 EIS(EZS)에 꽂는 크롬키·키리스고 키 모두 '스마트키'로 적었고, 폴딩키·카드키는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433MHz)만 적었습니다. 미국(315MHz) 사양 키(FCC IYZ3312·NBGDM3 등)는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2019(단종)' 형식입니다. 원본 목록 연식을 그대로 따랐습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">- 벤츠 키는 ID46 같은 일반 트랜스폰더가 아니라 NEC 프로세서 키(FBS3/FBS4)라서 'XT27A/A66·XT27B·XT57B 호환' 칸은 비어 있습니다(기아 파일 규칙상 해당 칩 없음). </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>- 이모빌라이저는 EIS(EZS, 전자식 점화 스위치 모듈)입니다. FBS3/FBS4 세대는 칩코드 칸에 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>- 키블레이드(키웨이)는 비상키 블레이드 HU64입니다(1997~2014 인서트 및 2019+ FBS4 비상키 모두 HU64 표기). 키블레이드 부품번호는 찾지 못해 비웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr"/>
+      <c r="A14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값, 또는 해당 연식 검색 자료가 없어 이전 연식 기준으로 채운 값 — 실물 키/VIN(SA코드 803/804 = FBS4)으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>- 전환 연식(FBS3→FBS4)은 색 없이 칩코드·이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: FBS3[2013.4 이전 생산], FBS4[2013.4 이후 생산]).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 검색했고 연식별 검색 기록은 research/benz/yearly.md에 있습니다. 같은 세대 안에서도 FBS3→FBS4 전환, 페이스리프트 후 신형 키 디자인, 키리스고 옵션 여부가 달라집니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>- 신형 키 디자인: E클래스 W213 2017~, S클래스 2018 페이스리프트~, G클래스 2019~, A·C·CLA·CLS·GLB·GLC·GLS 2020~(Gen3), GLE W167 2019~(티어드롭), 2021~ W223·W206·W214·X254·EQS/EQE는 MS5 계열 신형 키. 구형 키와 호환 안 됨.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>- 확인된 국내 사양(433/434MHz) 순정 품번: W205 A2059053609(3버튼)·A2059050000/A2059050600(2버튼), W222·C217·X222 A2229059610, W177 A1779057902, EQA·EQB A1779054606, FBS4 공용 보드 IYZDC12B.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>- FBS4 적용 시점: W212 2013.4~, 166(ML·GL)·207(E쿠페/카브리올레)·V212 2013.7~, 218(CLS) 2014.9~, 117(CLA)·156(GLA) 2014.11~, 172(SLK) 2015.4~, 205·217·222·231은 처음부터 FBS4. A클래스 W176은 2014년부터 FBS4.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>- FBS3 키는 로컬 장비(NEC/BGA 등)로 키 제작이 가능하지만, FBS4는 독일 벤츠 서버 인증이 필요해 사실상 딜러(또는 XENTRY 계정 보유 업체) 작업입니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>- 2021년 이후 신형(W206·W223·W214·X254·EQS/EQE 등)도 FBS4 딜러 전용으로 분류됩니다. 비상키는 Gen4 인서트(HU64).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>- FBS3/FBS4 키 구분: 키 기판 번호 문자열에 'K'가 앞에 있으면 FBS3 풀 스마트키, 중간에 있으면 FBS4 풀 스마트키. FBS4 기판에는 오른쪽에 트랜지스터가 있고 칩이 더 작습니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>- 순정 FBS4 스마트키(433MHz, 3버튼) IYZDC12B는 2014-2023년식 적용 표기, W222 S클래스 FBS4 키리스고 키 A2229059610(433MHz).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>- G클래스(W463) 구형: 2000~2001년식 키 자료 상충, 2002~2005년식 IR 스마트키·트랜스폰더 막대키 병존, 2006년식 검정 키, 2007년형부터 크롬 키, 2016년식 FBS3/FBS4 자료 상충.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n"/>
+      <c r="A29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n"/>
+      <c r="A37" s="13" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="n"/>
+      <c r="A46" s="13" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="n"/>
+      <c r="A50" s="13" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>- W246 FBS4는 2014.11 생산부터(EASYGUARD·abkeys W246 FBS4 EZS 2469057503) — 같은 MFA 플랫폼 W176·A45·CLA·GLA도 2014.11 전환으로 정리</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>- G클래스 W463 2002~: EIS(EZS) + 적외선 키(FBS3)로 바뀜(fixautosmart "G500 2002-2014 W463 EIS", CGDI MB G클래스 2003~ 적외선 모드) — 트랜스폰더 막대키는 2001년까지 DAS 차량</t>
         </is>

--- a/벤츠_models.xlsx
+++ b/벤츠_models.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -626,14 +629,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr"/>
-      <c r="L2" s="7" t="inlineStr"/>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M2" s="7" t="inlineStr"/>
       <c r="N2" s="7" t="inlineStr">
         <is>
@@ -676,14 +687,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I3" s="7" t="n"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K3" s="7" t="n"/>
-      <c r="L3" s="7" t="n"/>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M3" s="7" t="n"/>
       <c r="N3" s="10" t="inlineStr">
         <is>
@@ -726,14 +745,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I4" s="7" t="n"/>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K4" s="7" t="n"/>
-      <c r="L4" s="7" t="n"/>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M4" s="7" t="n"/>
       <c r="N4" s="10" t="inlineStr">
         <is>
@@ -776,7 +803,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -785,7 +816,7 @@
       <c r="K5" s="7" t="inlineStr"/>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr"/>
@@ -830,7 +861,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -839,7 +874,7 @@
       <c r="K6" s="7" t="inlineStr"/>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr"/>
@@ -884,7 +919,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -893,7 +932,7 @@
       <c r="K7" s="7" t="inlineStr"/>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr"/>
@@ -938,7 +977,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -947,7 +990,7 @@
       <c r="K8" s="7" t="inlineStr"/>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr"/>
@@ -1366,14 +1409,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="7" t="inlineStr">
         <is>
@@ -1416,14 +1467,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M17" s="7" t="n"/>
       <c r="N17" s="10" t="inlineStr">
         <is>
@@ -1466,14 +1525,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I18" s="7" t="n"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M18" s="7" t="n"/>
       <c r="N18" s="10" t="inlineStr">
         <is>
@@ -1516,7 +1583,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -1525,7 +1596,7 @@
       <c r="K19" s="7" t="inlineStr"/>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1570,7 +1641,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -1579,7 +1654,7 @@
       <c r="K20" s="7" t="inlineStr"/>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1624,7 +1699,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -1633,7 +1712,7 @@
       <c r="K21" s="7" t="inlineStr"/>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1678,7 +1757,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -1687,7 +1770,7 @@
       <c r="K22" s="7" t="inlineStr"/>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr"/>
@@ -2164,14 +2247,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="7" t="inlineStr">
         <is>
@@ -2214,14 +2305,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M32" s="7" t="inlineStr"/>
       <c r="N32" s="7" t="inlineStr">
         <is>
@@ -2264,14 +2363,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I33" s="7" t="n"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K33" s="7" t="n"/>
-      <c r="L33" s="7" t="n"/>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M33" s="7" t="n"/>
       <c r="N33" s="10" t="inlineStr">
         <is>
@@ -2314,14 +2421,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I34" s="7" t="n"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M34" s="7" t="n"/>
       <c r="N34" s="10" t="inlineStr">
         <is>
@@ -2364,7 +2479,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -2373,7 +2492,7 @@
       <c r="K35" s="7" t="inlineStr"/>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2418,14 +2537,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="7" t="inlineStr">
         <is>
@@ -2468,14 +2595,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I37" s="7" t="n"/>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M37" s="7" t="n"/>
       <c r="N37" s="7" t="inlineStr">
         <is>
@@ -2518,14 +2653,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I38" s="7" t="n"/>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K38" s="7" t="n"/>
-      <c r="L38" s="7" t="n"/>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M38" s="7" t="n"/>
       <c r="N38" s="7" t="inlineStr">
         <is>
@@ -2568,7 +2711,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -2577,7 +2724,7 @@
       <c r="K39" s="7" t="inlineStr"/>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2622,7 +2769,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -2631,7 +2782,7 @@
       <c r="K40" s="7" t="inlineStr"/>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2676,7 +2827,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -2685,7 +2840,7 @@
       <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2730,7 +2885,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -2739,7 +2898,7 @@
       <c r="K42" s="7" t="inlineStr"/>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2784,7 +2943,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -2793,7 +2956,7 @@
       <c r="K43" s="7" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr"/>
@@ -3138,14 +3301,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I50" s="7" t="n"/>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K50" s="7" t="n"/>
-      <c r="L50" s="7" t="n"/>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M50" s="7" t="n"/>
       <c r="N50" s="7" t="inlineStr">
         <is>
@@ -3188,14 +3359,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I51" s="7" t="n"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K51" s="7" t="n"/>
-      <c r="L51" s="7" t="n"/>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M51" s="7" t="n"/>
       <c r="N51" s="7" t="inlineStr">
         <is>
@@ -3238,7 +3417,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -3247,7 +3430,7 @@
       <c r="K52" s="7" t="inlineStr"/>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr"/>
@@ -3292,7 +3475,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -3301,7 +3488,7 @@
       <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr"/>
@@ -3346,7 +3533,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -3355,7 +3546,7 @@
       <c r="K54" s="7" t="inlineStr"/>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr"/>
@@ -3400,7 +3591,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -3409,7 +3604,7 @@
       <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr"/>
@@ -3454,7 +3649,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -3463,7 +3662,7 @@
       <c r="K56" s="7" t="inlineStr"/>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669055900[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr"/>
@@ -6546,14 +6745,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I114" s="7" t="inlineStr"/>
+      <c r="I114" s="7" t="inlineStr">
+        <is>
+          <t>A2037660106[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J114" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K114" s="7" t="inlineStr"/>
-      <c r="L114" s="7" t="n"/>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>A2037664906[해외 공용 품번], A2049050804[해외 공용 품번], A2117661606[키리스고, 해외 공용 품번], A2097660606[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M114" s="7" t="inlineStr"/>
       <c r="N114" s="7" t="inlineStr">
         <is>
@@ -6596,14 +6803,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I115" s="7" t="inlineStr"/>
+      <c r="I115" s="7" t="inlineStr">
+        <is>
+          <t>A2037660106[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J115" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K115" s="7" t="inlineStr"/>
-      <c r="L115" s="7" t="n"/>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>A2037664906[해외 공용 품번], A2049050804[해외 공용 품번], A2117661606[키리스고, 해외 공용 품번], A2097660606[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M115" s="7" t="inlineStr"/>
       <c r="N115" s="7" t="inlineStr">
         <is>
@@ -6646,14 +6861,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I116" s="7" t="inlineStr"/>
+      <c r="I116" s="7" t="inlineStr">
+        <is>
+          <t>A2037660106[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K116" s="7" t="inlineStr"/>
-      <c r="L116" s="7" t="n"/>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>A2037664906[해외 공용 품번], A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M116" s="7" t="inlineStr"/>
       <c r="N116" s="7" t="inlineStr">
         <is>
@@ -6696,14 +6919,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I117" s="7" t="inlineStr"/>
+      <c r="I117" s="7" t="inlineStr">
+        <is>
+          <t>A2037660106[해외 공용 품번], A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K117" s="7" t="inlineStr"/>
-      <c r="L117" s="7" t="n"/>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>A2037664906[해외 공용 품번], A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M117" s="7" t="inlineStr"/>
       <c r="N117" s="7" t="inlineStr">
         <is>
@@ -6746,14 +6977,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I118" s="7" t="inlineStr"/>
+      <c r="I118" s="7" t="inlineStr">
+        <is>
+          <t>A2037660106[해외 공용 품번], A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J118" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K118" s="7" t="inlineStr"/>
-      <c r="L118" s="7" t="n"/>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>A2037664906[해외 공용 품번], A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M118" s="7" t="inlineStr"/>
       <c r="N118" s="7" t="inlineStr">
         <is>
@@ -6796,14 +7035,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I119" s="7" t="inlineStr"/>
+      <c r="I119" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K119" s="7" t="inlineStr"/>
-      <c r="L119" s="7" t="n"/>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>A2037664906[해외 공용 품번], A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M119" s="7" t="inlineStr"/>
       <c r="N119" s="7" t="inlineStr">
         <is>
@@ -6846,14 +7093,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I120" s="7" t="inlineStr"/>
+      <c r="I120" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr"/>
-      <c r="L120" s="7" t="n"/>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>A2037664906[해외 공용 품번], A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M120" s="7" t="inlineStr"/>
       <c r="N120" s="7" t="inlineStr">
         <is>
@@ -6896,14 +7151,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I121" s="7" t="inlineStr"/>
+      <c r="I121" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J121" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K121" s="7" t="inlineStr"/>
-      <c r="L121" s="7" t="n"/>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>A2037664906[해외 공용 품번], A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M121" s="7" t="inlineStr"/>
       <c r="N121" s="7" t="inlineStr">
         <is>
@@ -6946,14 +7209,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I122" s="7" t="inlineStr"/>
+      <c r="I122" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J122" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K122" s="7" t="inlineStr"/>
-      <c r="L122" s="7" t="inlineStr"/>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M122" s="7" t="inlineStr"/>
       <c r="N122" s="7" t="inlineStr">
         <is>
@@ -6996,14 +7267,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I123" s="7" t="inlineStr"/>
+      <c r="I123" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J123" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K123" s="7" t="inlineStr"/>
-      <c r="L123" s="7" t="inlineStr"/>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M123" s="7" t="inlineStr"/>
       <c r="N123" s="7" t="inlineStr">
         <is>
@@ -7046,14 +7325,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I124" s="7" t="inlineStr"/>
+      <c r="I124" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K124" s="7" t="inlineStr"/>
-      <c r="L124" s="7" t="inlineStr"/>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M124" s="7" t="inlineStr"/>
       <c r="N124" s="7" t="inlineStr">
         <is>
@@ -7096,14 +7383,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I125" s="7" t="inlineStr"/>
+      <c r="I125" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J125" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K125" s="7" t="inlineStr"/>
-      <c r="L125" s="7" t="inlineStr"/>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M125" s="7" t="inlineStr"/>
       <c r="N125" s="7" t="inlineStr">
         <is>
@@ -7146,14 +7441,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I126" s="7" t="n"/>
+      <c r="I126" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K126" s="7" t="n"/>
-      <c r="L126" s="7" t="n"/>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="inlineStr">
         <is>
@@ -7196,14 +7499,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I127" s="7" t="n"/>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J127" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K127" s="7" t="n"/>
-      <c r="L127" s="7" t="n"/>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="inlineStr">
         <is>
@@ -7246,7 +7557,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I128" s="7" t="inlineStr"/>
+      <c r="I128" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J128" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -7255,7 +7570,7 @@
       <c r="K128" s="7" t="inlineStr"/>
       <c r="L128" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M128" s="7" t="inlineStr"/>
@@ -7300,7 +7615,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I129" s="7" t="inlineStr"/>
+      <c r="I129" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J129" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -7309,7 +7628,7 @@
       <c r="K129" s="7" t="inlineStr"/>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M129" s="7" t="inlineStr"/>
@@ -7354,7 +7673,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I130" s="7" t="inlineStr"/>
+      <c r="I130" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J130" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -7363,7 +7686,7 @@
       <c r="K130" s="7" t="inlineStr"/>
       <c r="L130" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M130" s="7" t="inlineStr"/>
@@ -8044,14 +8367,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I143" s="7" t="inlineStr"/>
+      <c r="I143" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J143" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K143" s="7" t="inlineStr"/>
-      <c r="L143" s="7" t="inlineStr"/>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M143" s="7" t="inlineStr"/>
       <c r="N143" s="7" t="inlineStr">
         <is>
@@ -8094,14 +8425,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I144" s="7" t="inlineStr"/>
+      <c r="I144" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J144" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K144" s="7" t="inlineStr"/>
-      <c r="L144" s="7" t="inlineStr"/>
+      <c r="L144" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M144" s="7" t="inlineStr"/>
       <c r="N144" s="7" t="inlineStr">
         <is>
@@ -8144,14 +8483,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I145" s="7" t="inlineStr"/>
+      <c r="I145" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J145" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K145" s="7" t="inlineStr"/>
-      <c r="L145" s="7" t="inlineStr"/>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M145" s="7" t="inlineStr"/>
       <c r="N145" s="7" t="inlineStr">
         <is>
@@ -8194,14 +8541,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I146" s="7" t="n"/>
+      <c r="I146" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J146" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K146" s="7" t="n"/>
-      <c r="L146" s="7" t="n"/>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M146" s="7" t="n"/>
       <c r="N146" s="7" t="inlineStr">
         <is>
@@ -8244,14 +8599,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I147" s="7" t="n"/>
+      <c r="I147" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J147" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K147" s="7" t="n"/>
-      <c r="L147" s="7" t="n"/>
+      <c r="L147" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M147" s="7" t="n"/>
       <c r="N147" s="7" t="inlineStr">
         <is>
@@ -8294,7 +8657,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I148" s="7" t="inlineStr"/>
+      <c r="I148" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J148" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -8303,7 +8670,7 @@
       <c r="K148" s="7" t="inlineStr"/>
       <c r="L148" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M148" s="7" t="inlineStr"/>
@@ -8348,7 +8715,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I149" s="7" t="inlineStr"/>
+      <c r="I149" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J149" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -8357,7 +8728,7 @@
       <c r="K149" s="7" t="inlineStr"/>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M149" s="7" t="inlineStr"/>
@@ -8402,7 +8773,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I150" s="7" t="inlineStr"/>
+      <c r="I150" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J150" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -8411,7 +8786,7 @@
       <c r="K150" s="7" t="inlineStr"/>
       <c r="L150" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M150" s="7" t="inlineStr"/>
@@ -8456,7 +8831,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I151" s="7" t="inlineStr"/>
+      <c r="I151" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J151" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -8465,7 +8844,7 @@
       <c r="K151" s="7" t="inlineStr"/>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M151" s="7" t="inlineStr"/>
@@ -8510,14 +8889,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I152" s="7" t="inlineStr"/>
+      <c r="I152" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J152" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K152" s="7" t="inlineStr"/>
-      <c r="L152" s="7" t="inlineStr"/>
+      <c r="L152" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M152" s="7" t="inlineStr"/>
       <c r="N152" s="7" t="inlineStr">
         <is>
@@ -8560,14 +8947,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I153" s="7" t="inlineStr"/>
+      <c r="I153" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J153" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K153" s="7" t="inlineStr"/>
-      <c r="L153" s="7" t="inlineStr"/>
+      <c r="L153" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M153" s="7" t="inlineStr"/>
       <c r="N153" s="7" t="inlineStr">
         <is>
@@ -8610,14 +9005,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I154" s="7" t="inlineStr"/>
+      <c r="I154" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J154" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K154" s="7" t="inlineStr"/>
-      <c r="L154" s="7" t="inlineStr"/>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M154" s="7" t="inlineStr"/>
       <c r="N154" s="7" t="inlineStr">
         <is>
@@ -8660,14 +9063,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I155" s="7" t="n"/>
+      <c r="I155" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J155" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K155" s="7" t="n"/>
-      <c r="L155" s="7" t="n"/>
+      <c r="L155" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M155" s="7" t="n"/>
       <c r="N155" s="7" t="inlineStr">
         <is>
@@ -8710,14 +9121,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I156" s="7" t="n"/>
+      <c r="I156" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J156" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K156" s="7" t="n"/>
-      <c r="L156" s="7" t="n"/>
+      <c r="L156" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M156" s="7" t="n"/>
       <c r="N156" s="7" t="inlineStr">
         <is>
@@ -8760,7 +9179,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I157" s="7" t="inlineStr"/>
+      <c r="I157" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J157" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -8769,7 +9192,7 @@
       <c r="K157" s="7" t="inlineStr"/>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M157" s="7" t="inlineStr"/>
@@ -8814,7 +9237,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I158" s="7" t="inlineStr"/>
+      <c r="I158" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J158" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -8823,7 +9250,7 @@
       <c r="K158" s="7" t="inlineStr"/>
       <c r="L158" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M158" s="7" t="inlineStr"/>
@@ -8868,7 +9295,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I159" s="7" t="inlineStr"/>
+      <c r="I159" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J159" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -8877,7 +9308,7 @@
       <c r="K159" s="7" t="inlineStr"/>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M159" s="7" t="inlineStr"/>
@@ -8922,7 +9353,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I160" s="7" t="inlineStr"/>
+      <c r="I160" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J160" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -8931,7 +9366,7 @@
       <c r="K160" s="7" t="inlineStr"/>
       <c r="L160" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2229055100[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M160" s="7" t="inlineStr"/>
@@ -8985,7 +9420,7 @@
       <c r="K161" s="7" t="inlineStr"/>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M161" s="7" t="inlineStr"/>
@@ -9039,7 +9474,7 @@
       <c r="K162" s="7" t="inlineStr"/>
       <c r="L162" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M162" s="7" t="inlineStr"/>
@@ -9093,7 +9528,7 @@
       <c r="K163" s="7" t="inlineStr"/>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M163" s="7" t="inlineStr"/>
@@ -9147,7 +9582,7 @@
       <c r="K164" s="7" t="inlineStr"/>
       <c r="L164" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M164" s="7" t="inlineStr"/>
@@ -9201,7 +9636,7 @@
       <c r="K165" s="7" t="inlineStr"/>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M165" s="7" t="inlineStr"/>
@@ -9255,7 +9690,7 @@
       <c r="K166" s="7" t="inlineStr"/>
       <c r="L166" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M166" s="7" t="inlineStr"/>
@@ -9309,7 +9744,7 @@
       <c r="K167" s="7" t="inlineStr"/>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M167" s="7" t="inlineStr"/>
@@ -9363,7 +9798,7 @@
       <c r="K168" s="7" t="inlineStr"/>
       <c r="L168" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M168" s="7" t="inlineStr"/>
@@ -9417,7 +9852,7 @@
       <c r="K169" s="7" t="inlineStr"/>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M169" s="7" t="inlineStr"/>
@@ -9471,7 +9906,7 @@
       <c r="K170" s="7" t="inlineStr"/>
       <c r="L170" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M170" s="7" t="inlineStr"/>
@@ -9525,7 +9960,7 @@
       <c r="K171" s="7" t="inlineStr"/>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M171" s="7" t="inlineStr"/>
@@ -9579,7 +10014,7 @@
       <c r="K172" s="7" t="inlineStr"/>
       <c r="L172" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M172" s="7" t="inlineStr"/>
@@ -9633,7 +10068,7 @@
       <c r="K173" s="7" t="inlineStr"/>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M173" s="7" t="inlineStr"/>
@@ -9687,7 +10122,7 @@
       <c r="K174" s="7" t="inlineStr"/>
       <c r="L174" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229056109[키리스고, 해외 공용 품번], A2389051902[옵션 B66, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M174" s="7" t="inlineStr"/>
@@ -10260,14 +10695,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I185" s="7" t="inlineStr"/>
+      <c r="I185" s="7" t="inlineStr">
+        <is>
+          <t>A2037660106[해외 공용 품번], A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J185" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K185" s="7" t="inlineStr"/>
-      <c r="L185" s="7" t="inlineStr"/>
+      <c r="L185" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번], A2037664906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M185" s="7" t="inlineStr"/>
       <c r="N185" s="7" t="inlineStr">
         <is>
@@ -10310,14 +10753,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I186" s="7" t="inlineStr"/>
+      <c r="I186" s="7" t="inlineStr">
+        <is>
+          <t>A2037660106[해외 공용 품번], A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J186" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K186" s="7" t="inlineStr"/>
-      <c r="L186" s="7" t="inlineStr"/>
+      <c r="L186" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번], A2037664906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M186" s="7" t="inlineStr"/>
       <c r="N186" s="7" t="inlineStr">
         <is>
@@ -10360,14 +10811,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I187" s="7" t="inlineStr"/>
+      <c r="I187" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J187" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K187" s="7" t="inlineStr"/>
-      <c r="L187" s="7" t="inlineStr"/>
+      <c r="L187" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번], A2037664906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M187" s="7" t="inlineStr"/>
       <c r="N187" s="7" t="inlineStr">
         <is>
@@ -10410,14 +10869,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I188" s="7" t="inlineStr"/>
+      <c r="I188" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J188" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K188" s="7" t="inlineStr"/>
-      <c r="L188" s="7" t="inlineStr"/>
+      <c r="L188" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번], A2037664906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M188" s="7" t="inlineStr"/>
       <c r="N188" s="7" t="inlineStr">
         <is>
@@ -10460,14 +10927,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I189" s="7" t="inlineStr"/>
+      <c r="I189" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J189" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K189" s="7" t="inlineStr"/>
-      <c r="L189" s="7" t="inlineStr"/>
+      <c r="L189" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번], A2037664906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M189" s="7" t="inlineStr"/>
       <c r="N189" s="7" t="inlineStr">
         <is>
@@ -10510,14 +10985,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I190" s="7" t="inlineStr"/>
+      <c r="I190" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J190" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K190" s="7" t="inlineStr"/>
-      <c r="L190" s="7" t="inlineStr"/>
+      <c r="L190" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2097660606[키리스고, 해외 공용 품번], A2037664906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M190" s="7" t="inlineStr"/>
       <c r="N190" s="7" t="inlineStr">
         <is>
@@ -10560,14 +11043,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I191" s="7" t="inlineStr"/>
+      <c r="I191" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J191" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K191" s="7" t="inlineStr"/>
-      <c r="L191" s="7" t="inlineStr"/>
+      <c r="L191" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M191" s="7" t="inlineStr"/>
       <c r="N191" s="7" t="inlineStr">
         <is>
@@ -10610,14 +11101,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I192" s="7" t="inlineStr"/>
+      <c r="I192" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J192" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K192" s="7" t="inlineStr"/>
-      <c r="L192" s="7" t="inlineStr"/>
+      <c r="L192" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M192" s="7" t="inlineStr"/>
       <c r="N192" s="7" t="inlineStr">
         <is>
@@ -10660,14 +11159,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I193" s="7" t="inlineStr"/>
+      <c r="I193" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J193" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K193" s="7" t="inlineStr"/>
-      <c r="L193" s="7" t="inlineStr"/>
+      <c r="L193" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M193" s="7" t="inlineStr"/>
       <c r="N193" s="7" t="inlineStr">
         <is>
@@ -10710,14 +11217,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I194" s="7" t="n"/>
+      <c r="I194" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J194" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K194" s="7" t="n"/>
-      <c r="L194" s="7" t="n"/>
+      <c r="L194" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M194" s="7" t="n"/>
       <c r="N194" s="7" t="inlineStr">
         <is>
@@ -10760,14 +11275,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I195" s="7" t="n"/>
+      <c r="I195" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J195" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K195" s="7" t="n"/>
-      <c r="L195" s="7" t="n"/>
+      <c r="L195" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M195" s="7" t="n"/>
       <c r="N195" s="7" t="inlineStr">
         <is>
@@ -10810,7 +11333,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I196" s="7" t="inlineStr"/>
+      <c r="I196" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J196" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -10819,7 +11346,7 @@
       <c r="K196" s="7" t="inlineStr"/>
       <c r="L196" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M196" s="7" t="inlineStr"/>
@@ -10864,7 +11391,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I197" s="7" t="inlineStr"/>
+      <c r="I197" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J197" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -10873,7 +11404,7 @@
       <c r="K197" s="7" t="inlineStr"/>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M197" s="7" t="inlineStr"/>
@@ -10918,7 +11449,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I198" s="7" t="inlineStr"/>
+      <c r="I198" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J198" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -10927,7 +11462,7 @@
       <c r="K198" s="7" t="inlineStr"/>
       <c r="L198" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M198" s="7" t="inlineStr"/>
@@ -11296,14 +11831,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I205" s="7" t="n"/>
+      <c r="I205" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J205" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K205" s="7" t="n"/>
-      <c r="L205" s="7" t="n"/>
+      <c r="L205" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M205" s="7" t="n"/>
       <c r="N205" s="7" t="inlineStr">
         <is>
@@ -11346,14 +11889,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I206" s="7" t="n"/>
+      <c r="I206" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J206" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K206" s="7" t="n"/>
-      <c r="L206" s="7" t="n"/>
+      <c r="L206" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M206" s="7" t="n"/>
       <c r="N206" s="7" t="inlineStr">
         <is>
@@ -11396,7 +11947,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I207" s="7" t="inlineStr"/>
+      <c r="I207" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J207" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -11405,7 +11960,7 @@
       <c r="K207" s="7" t="inlineStr"/>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M207" s="7" t="inlineStr"/>
@@ -11450,7 +12005,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I208" s="7" t="inlineStr"/>
+      <c r="I208" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J208" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -11459,7 +12018,7 @@
       <c r="K208" s="7" t="inlineStr"/>
       <c r="L208" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M208" s="7" t="inlineStr"/>
@@ -11504,7 +12063,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I209" s="7" t="inlineStr"/>
+      <c r="I209" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J209" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -11513,7 +12076,7 @@
       <c r="K209" s="7" t="inlineStr"/>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M209" s="7" t="inlineStr"/>
@@ -11558,7 +12121,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I210" s="7" t="inlineStr"/>
+      <c r="I210" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J210" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -11567,7 +12134,7 @@
       <c r="K210" s="7" t="inlineStr"/>
       <c r="L210" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2319054300[해외 공용 품번], A2229055008[해외 공용 품번], A2229055100[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M210" s="7" t="inlineStr"/>
@@ -11882,14 +12449,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I216" s="7" t="inlineStr"/>
+      <c r="I216" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J216" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K216" s="7" t="inlineStr"/>
-      <c r="L216" s="7" t="inlineStr"/>
+      <c r="L216" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M216" s="7" t="inlineStr"/>
       <c r="N216" s="10" t="inlineStr">
         <is>
@@ -11932,14 +12507,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I217" s="7" t="inlineStr"/>
+      <c r="I217" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J217" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K217" s="7" t="inlineStr"/>
-      <c r="L217" s="7" t="inlineStr"/>
+      <c r="L217" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M217" s="7" t="inlineStr"/>
       <c r="N217" s="7" t="inlineStr">
         <is>
@@ -11982,14 +12565,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I218" s="7" t="inlineStr"/>
+      <c r="I218" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J218" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K218" s="7" t="inlineStr"/>
-      <c r="L218" s="7" t="inlineStr"/>
+      <c r="L218" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M218" s="7" t="inlineStr"/>
       <c r="N218" s="7" t="inlineStr">
         <is>
@@ -12032,14 +12623,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I219" s="7" t="inlineStr"/>
+      <c r="I219" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J219" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K219" s="7" t="inlineStr"/>
-      <c r="L219" s="7" t="inlineStr"/>
+      <c r="L219" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M219" s="7" t="inlineStr"/>
       <c r="N219" s="7" t="inlineStr">
         <is>
@@ -12082,14 +12681,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I220" s="7" t="inlineStr"/>
+      <c r="I220" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J220" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K220" s="7" t="inlineStr"/>
-      <c r="L220" s="7" t="inlineStr"/>
+      <c r="L220" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M220" s="7" t="inlineStr"/>
       <c r="N220" s="7" t="inlineStr">
         <is>
@@ -12132,14 +12739,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I221" s="7" t="inlineStr"/>
+      <c r="I221" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J221" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K221" s="7" t="inlineStr"/>
-      <c r="L221" s="7" t="inlineStr"/>
+      <c r="L221" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M221" s="7" t="inlineStr"/>
       <c r="N221" s="7" t="inlineStr">
         <is>
@@ -12189,7 +12804,11 @@
         </is>
       </c>
       <c r="K222" s="7" t="inlineStr"/>
-      <c r="L222" s="7" t="inlineStr"/>
+      <c r="L222" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M222" s="7" t="inlineStr"/>
       <c r="N222" s="7" t="inlineStr">
         <is>
@@ -12239,7 +12858,11 @@
         </is>
       </c>
       <c r="K223" s="7" t="inlineStr"/>
-      <c r="L223" s="7" t="inlineStr"/>
+      <c r="L223" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M223" s="7" t="inlineStr"/>
       <c r="N223" s="7" t="inlineStr">
         <is>
@@ -12289,7 +12912,11 @@
         </is>
       </c>
       <c r="K224" s="7" t="inlineStr"/>
-      <c r="L224" s="7" t="inlineStr"/>
+      <c r="L224" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M224" s="7" t="inlineStr"/>
       <c r="N224" s="7" t="inlineStr">
         <is>
@@ -15112,14 +15739,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I277" s="7" t="n"/>
+      <c r="I277" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J277" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K277" s="7" t="n"/>
-      <c r="L277" s="7" t="n"/>
+      <c r="L277" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M277" s="7" t="n"/>
       <c r="N277" s="7" t="inlineStr">
         <is>
@@ -15162,14 +15797,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I278" s="7" t="n"/>
+      <c r="I278" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J278" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K278" s="7" t="n"/>
-      <c r="L278" s="7" t="n"/>
+      <c r="L278" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M278" s="7" t="n"/>
       <c r="N278" s="7" t="inlineStr">
         <is>
@@ -15212,7 +15855,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I279" s="7" t="inlineStr"/>
+      <c r="I279" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J279" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -15221,7 +15868,7 @@
       <c r="K279" s="7" t="inlineStr"/>
       <c r="L279" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M279" s="7" t="inlineStr"/>
@@ -15266,7 +15913,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I280" s="7" t="inlineStr"/>
+      <c r="I280" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J280" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -15275,7 +15926,7 @@
       <c r="K280" s="7" t="inlineStr"/>
       <c r="L280" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M280" s="7" t="inlineStr"/>
@@ -15320,7 +15971,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I281" s="7" t="inlineStr"/>
+      <c r="I281" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J281" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -15329,7 +15984,7 @@
       <c r="K281" s="7" t="inlineStr"/>
       <c r="L281" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M281" s="7" t="inlineStr"/>
@@ -15374,7 +16029,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I282" s="7" t="inlineStr"/>
+      <c r="I282" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J282" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -15383,7 +16042,7 @@
       <c r="K282" s="7" t="inlineStr"/>
       <c r="L282" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M282" s="7" t="inlineStr"/>
@@ -15428,7 +16087,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I283" s="7" t="inlineStr"/>
+      <c r="I283" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J283" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -15437,7 +16100,7 @@
       <c r="K283" s="7" t="inlineStr"/>
       <c r="L283" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M283" s="7" t="inlineStr"/>
@@ -15482,7 +16145,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I284" s="7" t="inlineStr"/>
+      <c r="I284" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J284" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -15491,7 +16158,7 @@
       <c r="K284" s="7" t="inlineStr"/>
       <c r="L284" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M284" s="7" t="inlineStr"/>
@@ -15886,14 +16553,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I292" s="7" t="n"/>
+      <c r="I292" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J292" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K292" s="7" t="n"/>
-      <c r="L292" s="7" t="n"/>
+      <c r="L292" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M292" s="7" t="n"/>
       <c r="N292" s="7" t="inlineStr">
         <is>
@@ -15936,14 +16611,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I293" s="7" t="n"/>
+      <c r="I293" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J293" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K293" s="7" t="n"/>
-      <c r="L293" s="7" t="n"/>
+      <c r="L293" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M293" s="7" t="n"/>
       <c r="N293" s="7" t="inlineStr">
         <is>
@@ -15986,7 +16669,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I294" s="7" t="inlineStr"/>
+      <c r="I294" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J294" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -15995,7 +16682,7 @@
       <c r="K294" s="7" t="inlineStr"/>
       <c r="L294" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M294" s="7" t="inlineStr"/>
@@ -16040,7 +16727,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I295" s="7" t="inlineStr"/>
+      <c r="I295" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J295" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -16049,7 +16740,7 @@
       <c r="K295" s="7" t="inlineStr"/>
       <c r="L295" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M295" s="7" t="inlineStr"/>
@@ -16094,7 +16785,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I296" s="7" t="inlineStr"/>
+      <c r="I296" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J296" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -16103,7 +16798,7 @@
       <c r="K296" s="7" t="inlineStr"/>
       <c r="L296" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M296" s="7" t="inlineStr"/>
@@ -16148,7 +16843,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I297" s="7" t="inlineStr"/>
+      <c r="I297" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J297" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -16157,7 +16856,7 @@
       <c r="K297" s="7" t="inlineStr"/>
       <c r="L297" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M297" s="7" t="inlineStr"/>
@@ -16202,7 +16901,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I298" s="7" t="inlineStr"/>
+      <c r="I298" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J298" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -16211,7 +16914,7 @@
       <c r="K298" s="7" t="inlineStr"/>
       <c r="L298" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M298" s="7" t="inlineStr"/>
@@ -16256,14 +16959,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I299" s="7" t="inlineStr"/>
+      <c r="I299" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J299" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K299" s="7" t="inlineStr"/>
-      <c r="L299" s="7" t="n"/>
+      <c r="L299" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A2059050600[해외 공용 품번], A1669055900[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[키리스고, 해외 공용 품번], A2059051411[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M299" s="7" t="inlineStr"/>
       <c r="N299" s="7" t="inlineStr">
         <is>
@@ -17256,14 +17967,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I319" s="7" t="inlineStr"/>
+      <c r="I319" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J319" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K319" s="7" t="inlineStr"/>
-      <c r="L319" s="7" t="inlineStr"/>
+      <c r="L319" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2127666006[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M319" s="7" t="inlineStr"/>
       <c r="N319" s="7" t="inlineStr">
         <is>
@@ -17306,14 +18025,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I320" s="7" t="inlineStr"/>
+      <c r="I320" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J320" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K320" s="7" t="inlineStr"/>
-      <c r="L320" s="7" t="inlineStr"/>
+      <c r="L320" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2127666006[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M320" s="7" t="inlineStr"/>
       <c r="N320" s="7" t="inlineStr">
         <is>
@@ -17356,14 +18083,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I321" s="7" t="inlineStr"/>
+      <c r="I321" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J321" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K321" s="7" t="inlineStr"/>
-      <c r="L321" s="7" t="inlineStr"/>
+      <c r="L321" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M321" s="7" t="inlineStr"/>
       <c r="N321" s="7" t="inlineStr">
         <is>
@@ -17406,14 +18141,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I322" s="7" t="inlineStr"/>
+      <c r="I322" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J322" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K322" s="7" t="inlineStr"/>
-      <c r="L322" s="7" t="inlineStr"/>
+      <c r="L322" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M322" s="7" t="inlineStr"/>
       <c r="N322" s="7" t="inlineStr">
         <is>
@@ -17456,14 +18199,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I323" s="7" t="inlineStr"/>
+      <c r="I323" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J323" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K323" s="7" t="inlineStr"/>
-      <c r="L323" s="7" t="inlineStr"/>
+      <c r="L323" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M323" s="7" t="inlineStr"/>
       <c r="N323" s="7" t="inlineStr">
         <is>
@@ -17506,14 +18257,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I324" s="7" t="inlineStr"/>
+      <c r="I324" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J324" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K324" s="7" t="inlineStr"/>
-      <c r="L324" s="7" t="inlineStr"/>
+      <c r="L324" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M324" s="7" t="inlineStr"/>
       <c r="N324" s="7" t="inlineStr">
         <is>
@@ -17556,14 +18315,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I325" s="7" t="n"/>
+      <c r="I325" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J325" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K325" s="7" t="n"/>
-      <c r="L325" s="7" t="n"/>
+      <c r="L325" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M325" s="7" t="n"/>
       <c r="N325" s="10" t="inlineStr">
         <is>
@@ -17606,14 +18373,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I326" s="7" t="n"/>
+      <c r="I326" s="7" t="inlineStr">
+        <is>
+          <t>A2037665006[해외 공용 품번], A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J326" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K326" s="7" t="n"/>
-      <c r="L326" s="7" t="n"/>
+      <c r="L326" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M326" s="7" t="n"/>
       <c r="N326" s="10" t="inlineStr">
         <is>
@@ -17656,7 +18431,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I327" s="7" t="inlineStr"/>
+      <c r="I327" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J327" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -17665,7 +18444,7 @@
       <c r="K327" s="7" t="inlineStr"/>
       <c r="L327" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M327" s="7" t="inlineStr"/>
@@ -17710,7 +18489,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I328" s="7" t="inlineStr"/>
+      <c r="I328" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J328" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -17719,7 +18502,7 @@
       <c r="K328" s="7" t="inlineStr"/>
       <c r="L328" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M328" s="7" t="inlineStr"/>
@@ -17764,7 +18547,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I329" s="7" t="inlineStr"/>
+      <c r="I329" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J329" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -17773,7 +18560,7 @@
       <c r="K329" s="7" t="inlineStr"/>
       <c r="L329" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M329" s="7" t="inlineStr"/>
@@ -17818,7 +18605,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I330" s="7" t="inlineStr"/>
+      <c r="I330" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J330" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -17827,7 +18618,7 @@
       <c r="K330" s="7" t="inlineStr"/>
       <c r="L330" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M330" s="7" t="inlineStr"/>
@@ -17872,7 +18663,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I331" s="7" t="inlineStr"/>
+      <c r="I331" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J331" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -17881,7 +18676,7 @@
       <c r="K331" s="7" t="inlineStr"/>
       <c r="L331" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M331" s="7" t="inlineStr"/>
@@ -17926,7 +18721,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I332" s="7" t="inlineStr"/>
+      <c r="I332" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J332" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -17935,7 +18734,7 @@
       <c r="K332" s="7" t="inlineStr"/>
       <c r="L332" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M332" s="7" t="inlineStr"/>
@@ -17980,7 +18779,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I333" s="7" t="inlineStr"/>
+      <c r="I333" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J333" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -17989,7 +18792,7 @@
       <c r="K333" s="7" t="inlineStr"/>
       <c r="L333" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M333" s="7" t="inlineStr"/>
@@ -18234,7 +19037,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I338" s="7" t="inlineStr"/>
+      <c r="I338" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J338" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -18243,7 +19050,7 @@
       <c r="K338" s="7" t="inlineStr"/>
       <c r="L338" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M338" s="7" t="inlineStr"/>
@@ -18288,7 +19095,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I339" s="7" t="inlineStr"/>
+      <c r="I339" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J339" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -18297,7 +19108,7 @@
       <c r="K339" s="7" t="inlineStr"/>
       <c r="L339" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M339" s="7" t="inlineStr"/>
@@ -18342,7 +19153,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I340" s="7" t="inlineStr"/>
+      <c r="I340" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J340" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -18351,7 +19166,7 @@
       <c r="K340" s="7" t="inlineStr"/>
       <c r="L340" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M340" s="7" t="inlineStr"/>
@@ -18396,7 +19211,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I341" s="7" t="inlineStr"/>
+      <c r="I341" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J341" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -18405,7 +19224,7 @@
       <c r="K341" s="7" t="inlineStr"/>
       <c r="L341" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M341" s="7" t="inlineStr"/>
@@ -18450,7 +19269,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I342" s="7" t="inlineStr"/>
+      <c r="I342" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J342" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -18459,7 +19282,7 @@
       <c r="K342" s="7" t="inlineStr"/>
       <c r="L342" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M342" s="7" t="inlineStr"/>
@@ -18504,7 +19327,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I343" s="7" t="inlineStr"/>
+      <c r="I343" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J343" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -18513,7 +19340,7 @@
       <c r="K343" s="7" t="inlineStr"/>
       <c r="L343" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M343" s="7" t="inlineStr"/>
@@ -18558,7 +19385,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I344" s="7" t="inlineStr"/>
+      <c r="I344" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J344" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -18567,7 +19398,7 @@
       <c r="K344" s="7" t="inlineStr"/>
       <c r="L344" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229054100[해외 공용 품번], A2059050600[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2059051411[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M344" s="7" t="inlineStr"/>
@@ -18769,7 +19600,11 @@
         </is>
       </c>
       <c r="K348" s="7" t="inlineStr"/>
-      <c r="L348" s="7" t="inlineStr"/>
+      <c r="L348" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M348" s="7" t="inlineStr"/>
       <c r="N348" s="10" t="inlineStr">
         <is>
@@ -18819,7 +19654,11 @@
         </is>
       </c>
       <c r="K349" s="7" t="inlineStr"/>
-      <c r="L349" s="7" t="inlineStr"/>
+      <c r="L349" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M349" s="7" t="inlineStr"/>
       <c r="N349" s="7" t="inlineStr">
         <is>
@@ -18869,7 +19708,11 @@
         </is>
       </c>
       <c r="K350" s="7" t="inlineStr"/>
-      <c r="L350" s="7" t="inlineStr"/>
+      <c r="L350" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M350" s="7" t="inlineStr"/>
       <c r="N350" s="7" t="inlineStr">
         <is>
@@ -18919,7 +19762,11 @@
         </is>
       </c>
       <c r="K351" s="7" t="inlineStr"/>
-      <c r="L351" s="7" t="inlineStr"/>
+      <c r="L351" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M351" s="7" t="inlineStr"/>
       <c r="N351" s="7" t="inlineStr">
         <is>
@@ -18969,7 +19816,11 @@
         </is>
       </c>
       <c r="K352" s="7" t="inlineStr"/>
-      <c r="L352" s="7" t="inlineStr"/>
+      <c r="L352" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M352" s="7" t="inlineStr"/>
       <c r="N352" s="7" t="inlineStr">
         <is>
@@ -19019,7 +19870,11 @@
         </is>
       </c>
       <c r="K353" s="7" t="inlineStr"/>
-      <c r="L353" s="7" t="inlineStr"/>
+      <c r="L353" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M353" s="7" t="inlineStr"/>
       <c r="N353" s="7" t="inlineStr">
         <is>
@@ -19069,7 +19924,11 @@
         </is>
       </c>
       <c r="K354" s="7" t="inlineStr"/>
-      <c r="L354" s="7" t="inlineStr"/>
+      <c r="L354" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M354" s="7" t="inlineStr"/>
       <c r="N354" s="7" t="inlineStr">
         <is>
@@ -19119,7 +19978,11 @@
         </is>
       </c>
       <c r="K355" s="7" t="inlineStr"/>
-      <c r="L355" s="7" t="inlineStr"/>
+      <c r="L355" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M355" s="7" t="inlineStr"/>
       <c r="N355" s="7" t="inlineStr">
         <is>
@@ -19162,14 +20025,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I356" s="7" t="inlineStr"/>
+      <c r="I356" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J356" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K356" s="7" t="inlineStr"/>
-      <c r="L356" s="7" t="inlineStr"/>
+      <c r="L356" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051500[키리스고, 해외 공용 품번], A2229055100[해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M356" s="7" t="inlineStr"/>
       <c r="N356" s="7" t="inlineStr">
         <is>
@@ -19212,14 +20083,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I357" s="7" t="n"/>
+      <c r="I357" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J357" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K357" s="7" t="n"/>
-      <c r="L357" s="7" t="n"/>
+      <c r="L357" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051500[키리스고, 해외 공용 품번], A2229055100[해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M357" s="7" t="n"/>
       <c r="N357" s="7" t="inlineStr">
         <is>
@@ -19262,14 +20141,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I358" s="7" t="n"/>
+      <c r="I358" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J358" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K358" s="7" t="n"/>
-      <c r="L358" s="7" t="n"/>
+      <c r="L358" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051500[키리스고, 해외 공용 품번], A2229055100[해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M358" s="7" t="n"/>
       <c r="N358" s="7" t="inlineStr">
         <is>
@@ -19312,7 +20199,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I359" s="7" t="inlineStr"/>
+      <c r="I359" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J359" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -19321,7 +20212,7 @@
       <c r="K359" s="7" t="inlineStr"/>
       <c r="L359" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051500[키리스고, 해외 공용 품번], A2059059404[해외 공용 품번], A2229055100[해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M359" s="7" t="inlineStr"/>
@@ -19366,7 +20257,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I360" s="7" t="inlineStr"/>
+      <c r="I360" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J360" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -19375,7 +20270,7 @@
       <c r="K360" s="7" t="inlineStr"/>
       <c r="L360" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M360" s="7" t="inlineStr"/>
@@ -19420,7 +20315,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I361" s="7" t="inlineStr"/>
+      <c r="I361" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J361" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -19429,7 +20328,7 @@
       <c r="K361" s="7" t="inlineStr"/>
       <c r="L361" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번], A2059059404[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M361" s="7" t="inlineStr"/>
@@ -19474,7 +20373,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I362" s="7" t="inlineStr"/>
+      <c r="I362" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J362" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -19483,7 +20386,7 @@
       <c r="K362" s="7" t="inlineStr"/>
       <c r="L362" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번], A2059059404[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M362" s="7" t="inlineStr"/>
@@ -19528,7 +20431,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I363" s="7" t="inlineStr"/>
+      <c r="I363" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J363" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -19537,7 +20444,7 @@
       <c r="K363" s="7" t="inlineStr"/>
       <c r="L363" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번], A2059059404[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M363" s="7" t="inlineStr"/>
@@ -19582,7 +20489,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I364" s="7" t="inlineStr"/>
+      <c r="I364" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J364" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -19591,7 +20502,7 @@
       <c r="K364" s="7" t="inlineStr"/>
       <c r="L364" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번], A2059059404[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M364" s="7" t="inlineStr"/>
@@ -20068,7 +20979,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I373" s="7" t="inlineStr"/>
+      <c r="I373" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J373" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -20077,7 +20992,7 @@
       <c r="K373" s="7" t="inlineStr"/>
       <c r="L373" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번], A2059059404[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M373" s="7" t="inlineStr"/>
@@ -20122,7 +21037,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I374" s="7" t="inlineStr"/>
+      <c r="I374" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J374" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -20131,7 +21050,7 @@
       <c r="K374" s="7" t="inlineStr"/>
       <c r="L374" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번], A2059059404[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M374" s="7" t="inlineStr"/>
@@ -20176,7 +21095,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I375" s="7" t="inlineStr"/>
+      <c r="I375" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J375" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -20185,7 +21108,7 @@
       <c r="K375" s="7" t="inlineStr"/>
       <c r="L375" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번], A2059059404[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M375" s="7" t="inlineStr"/>
@@ -20230,7 +21153,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I376" s="7" t="inlineStr"/>
+      <c r="I376" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J376" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -20239,7 +21166,7 @@
       <c r="K376" s="7" t="inlineStr"/>
       <c r="L376" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번], A2059059404[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M376" s="7" t="inlineStr"/>
@@ -20669,7 +21596,11 @@
         </is>
       </c>
       <c r="K384" s="7" t="inlineStr"/>
-      <c r="L384" s="7" t="inlineStr"/>
+      <c r="L384" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M384" s="7" t="inlineStr"/>
       <c r="N384" s="7" t="inlineStr">
         <is>
@@ -20719,7 +21650,11 @@
         </is>
       </c>
       <c r="K385" s="7" t="inlineStr"/>
-      <c r="L385" s="7" t="inlineStr"/>
+      <c r="L385" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M385" s="7" t="inlineStr"/>
       <c r="N385" s="7" t="inlineStr">
         <is>
@@ -20769,7 +21704,11 @@
         </is>
       </c>
       <c r="K386" s="7" t="inlineStr"/>
-      <c r="L386" s="7" t="inlineStr"/>
+      <c r="L386" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M386" s="7" t="inlineStr"/>
       <c r="N386" s="7" t="inlineStr">
         <is>
@@ -20812,14 +21751,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I387" s="7" t="inlineStr"/>
+      <c r="I387" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J387" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K387" s="7" t="inlineStr"/>
-      <c r="L387" s="7" t="inlineStr"/>
+      <c r="L387" s="7" t="inlineStr">
+        <is>
+          <t>A9069058900[해외 공용 품번], A2049051704[해외 공용 품번], A2049050804[해외 공용 품번], A2517660706[키리스고, 해외 공용 품번], A2309050639[키리스고, 해외 공용 품번], A2049056802[키리스고, 해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051500[키리스고, 해외 공용 품번], A2229055100[해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M387" s="7" t="inlineStr"/>
       <c r="N387" s="7" t="inlineStr">
         <is>
@@ -20862,14 +21809,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I388" s="7" t="n"/>
+      <c r="I388" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J388" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K388" s="7" t="n"/>
-      <c r="L388" s="7" t="n"/>
+      <c r="L388" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051500[키리스고, 해외 공용 품번], A2229055100[해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M388" s="7" t="n"/>
       <c r="N388" s="7" t="inlineStr">
         <is>
@@ -20912,14 +21867,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I389" s="7" t="n"/>
+      <c r="I389" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J389" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K389" s="7" t="n"/>
-      <c r="L389" s="7" t="n"/>
+      <c r="L389" s="7" t="inlineStr">
+        <is>
+          <t>A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051500[키리스고, 해외 공용 품번], A2229055100[해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M389" s="7" t="n"/>
       <c r="N389" s="7" t="inlineStr">
         <is>
@@ -20962,7 +21925,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I390" s="7" t="inlineStr"/>
+      <c r="I390" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J390" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -20971,7 +21938,7 @@
       <c r="K390" s="7" t="inlineStr"/>
       <c r="L390" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051500[키리스고, 해외 공용 품번], A2059059404[해외 공용 품번], A2229055100[해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M390" s="7" t="inlineStr"/>
@@ -21016,7 +21983,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I391" s="7" t="inlineStr"/>
+      <c r="I391" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J391" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -21025,7 +21996,7 @@
       <c r="K391" s="7" t="inlineStr"/>
       <c r="L391" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059059404[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M391" s="7" t="inlineStr"/>
@@ -21070,7 +22041,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I392" s="7" t="inlineStr"/>
+      <c r="I392" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J392" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -21079,7 +22054,7 @@
       <c r="K392" s="7" t="inlineStr"/>
       <c r="L392" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M392" s="7" t="inlineStr"/>
@@ -21124,7 +22099,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I393" s="7" t="inlineStr"/>
+      <c r="I393" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J393" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -21133,7 +22112,7 @@
       <c r="K393" s="7" t="inlineStr"/>
       <c r="L393" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M393" s="7" t="inlineStr"/>
@@ -21178,7 +22157,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I394" s="7" t="inlineStr"/>
+      <c r="I394" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J394" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -21187,7 +22170,7 @@
       <c r="K394" s="7" t="inlineStr"/>
       <c r="L394" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M394" s="7" t="inlineStr"/>
@@ -21232,7 +22215,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I395" s="7" t="inlineStr"/>
+      <c r="I395" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J395" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -21241,7 +22228,7 @@
       <c r="K395" s="7" t="inlineStr"/>
       <c r="L395" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M395" s="7" t="inlineStr"/>
@@ -21286,7 +22273,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I396" s="7" t="inlineStr"/>
+      <c r="I396" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J396" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -21295,7 +22286,7 @@
       <c r="K396" s="7" t="inlineStr"/>
       <c r="L396" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A1669056800[해외 공용 품번], A1669055900[해외 공용 품번], A1667662506[키리스고, 해외 공용 품번], A1667661906[키리스고, 해외 공용 품번], A2059050600[해외 공용 품번], A2229054100[해외 공용 품번], A2059051411[해외 공용 품번], A2229055008[키리스고, 해외 공용 품번], A2229055400[해외 공용 품번], A2229050105[해외 공용 품번], A2229055108[해외 공용 품번], A2229055208[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M396" s="7" t="inlineStr"/>
@@ -22047,7 +23038,11 @@
         </is>
       </c>
       <c r="K411" s="7" t="inlineStr"/>
-      <c r="L411" s="7" t="inlineStr"/>
+      <c r="L411" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M411" s="7" t="inlineStr"/>
       <c r="N411" s="4" t="inlineStr">
         <is>
@@ -22101,7 +23096,11 @@
         </is>
       </c>
       <c r="K412" s="7" t="inlineStr"/>
-      <c r="L412" s="7" t="inlineStr"/>
+      <c r="L412" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M412" s="7" t="inlineStr"/>
       <c r="N412" s="4" t="inlineStr">
         <is>
@@ -22155,7 +23154,11 @@
         </is>
       </c>
       <c r="K413" s="7" t="inlineStr"/>
-      <c r="L413" s="7" t="n"/>
+      <c r="L413" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M413" s="7" t="inlineStr"/>
       <c r="N413" s="10" t="inlineStr">
         <is>
@@ -22205,7 +23208,11 @@
         </is>
       </c>
       <c r="K414" s="7" t="inlineStr"/>
-      <c r="L414" s="7" t="n"/>
+      <c r="L414" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M414" s="7" t="inlineStr"/>
       <c r="N414" s="10" t="inlineStr">
         <is>
@@ -22255,7 +23262,11 @@
         </is>
       </c>
       <c r="K415" s="7" t="inlineStr"/>
-      <c r="L415" s="7" t="n"/>
+      <c r="L415" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M415" s="7" t="inlineStr"/>
       <c r="N415" s="10" t="inlineStr">
         <is>
@@ -22305,7 +23316,11 @@
         </is>
       </c>
       <c r="K416" s="7" t="inlineStr"/>
-      <c r="L416" s="7" t="n"/>
+      <c r="L416" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M416" s="7" t="inlineStr"/>
       <c r="N416" s="10" t="inlineStr">
         <is>
@@ -22355,7 +23370,11 @@
         </is>
       </c>
       <c r="K417" s="7" t="inlineStr"/>
-      <c r="L417" s="7" t="n"/>
+      <c r="L417" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M417" s="7" t="inlineStr"/>
       <c r="N417" s="7" t="inlineStr">
         <is>
@@ -22405,7 +23424,11 @@
         </is>
       </c>
       <c r="K418" s="7" t="inlineStr"/>
-      <c r="L418" s="7" t="n"/>
+      <c r="L418" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M418" s="7" t="inlineStr"/>
       <c r="N418" s="7" t="inlineStr">
         <is>
@@ -22455,7 +23478,11 @@
         </is>
       </c>
       <c r="K419" s="7" t="inlineStr"/>
-      <c r="L419" s="7" t="n"/>
+      <c r="L419" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M419" s="7" t="inlineStr"/>
       <c r="N419" s="7" t="inlineStr">
         <is>
@@ -22505,7 +23532,11 @@
         </is>
       </c>
       <c r="K420" s="7" t="inlineStr"/>
-      <c r="L420" s="7" t="n"/>
+      <c r="L420" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M420" s="7" t="inlineStr"/>
       <c r="N420" s="7" t="inlineStr">
         <is>
@@ -22555,7 +23586,11 @@
         </is>
       </c>
       <c r="K421" s="7" t="inlineStr"/>
-      <c r="L421" s="7" t="n"/>
+      <c r="L421" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M421" s="7" t="inlineStr"/>
       <c r="N421" s="7" t="inlineStr">
         <is>
@@ -22605,7 +23640,11 @@
         </is>
       </c>
       <c r="K422" s="7" t="inlineStr"/>
-      <c r="L422" s="7" t="n"/>
+      <c r="L422" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M422" s="7" t="inlineStr"/>
       <c r="N422" s="7" t="inlineStr">
         <is>
@@ -22655,7 +23694,11 @@
         </is>
       </c>
       <c r="K423" s="7" t="inlineStr"/>
-      <c r="L423" s="7" t="n"/>
+      <c r="L423" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M423" s="7" t="inlineStr"/>
       <c r="N423" s="7" t="inlineStr">
         <is>
@@ -22705,7 +23748,11 @@
         </is>
       </c>
       <c r="K424" s="7" t="inlineStr"/>
-      <c r="L424" s="7" t="n"/>
+      <c r="L424" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M424" s="7" t="inlineStr"/>
       <c r="N424" s="7" t="inlineStr">
         <is>
@@ -22755,7 +23802,11 @@
         </is>
       </c>
       <c r="K425" s="7" t="inlineStr"/>
-      <c r="L425" s="7" t="n"/>
+      <c r="L425" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M425" s="7" t="inlineStr"/>
       <c r="N425" s="7" t="inlineStr">
         <is>
@@ -22805,7 +23856,11 @@
         </is>
       </c>
       <c r="K426" s="7" t="inlineStr"/>
-      <c r="L426" s="7" t="n"/>
+      <c r="L426" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M426" s="7" t="inlineStr"/>
       <c r="N426" s="7" t="inlineStr">
         <is>
@@ -22855,7 +23910,11 @@
         </is>
       </c>
       <c r="K427" s="7" t="n"/>
-      <c r="L427" s="7" t="n"/>
+      <c r="L427" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M427" s="7" t="n"/>
       <c r="N427" s="4" t="inlineStr">
         <is>
@@ -22909,7 +23968,11 @@
         </is>
       </c>
       <c r="K428" s="7" t="n"/>
-      <c r="L428" s="7" t="n"/>
+      <c r="L428" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M428" s="7" t="n"/>
       <c r="N428" s="4" t="inlineStr">
         <is>
@@ -22965,7 +24028,7 @@
       <c r="K429" s="7" t="inlineStr"/>
       <c r="L429" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M429" s="7" t="inlineStr"/>
@@ -23019,7 +24082,7 @@
       <c r="K430" s="7" t="inlineStr"/>
       <c r="L430" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M430" s="7" t="inlineStr"/>
@@ -23521,7 +24584,11 @@
         </is>
       </c>
       <c r="K440" s="7" t="inlineStr"/>
-      <c r="L440" s="7" t="n"/>
+      <c r="L440" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M440" s="7" t="inlineStr"/>
       <c r="N440" s="7" t="inlineStr">
         <is>
@@ -23571,7 +24638,11 @@
         </is>
       </c>
       <c r="K441" s="7" t="inlineStr"/>
-      <c r="L441" s="7" t="n"/>
+      <c r="L441" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M441" s="7" t="inlineStr"/>
       <c r="N441" s="7" t="inlineStr">
         <is>
@@ -23621,7 +24692,11 @@
         </is>
       </c>
       <c r="K442" s="7" t="inlineStr"/>
-      <c r="L442" s="7" t="n"/>
+      <c r="L442" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M442" s="7" t="inlineStr"/>
       <c r="N442" s="7" t="inlineStr">
         <is>
@@ -23671,7 +24746,11 @@
         </is>
       </c>
       <c r="K443" s="7" t="n"/>
-      <c r="L443" s="7" t="n"/>
+      <c r="L443" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M443" s="7" t="n"/>
       <c r="N443" s="4" t="inlineStr">
         <is>
@@ -23725,7 +24804,11 @@
         </is>
       </c>
       <c r="K444" s="7" t="n"/>
-      <c r="L444" s="7" t="n"/>
+      <c r="L444" s="7" t="inlineStr">
+        <is>
+          <t>A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M444" s="7" t="n"/>
       <c r="N444" s="4" t="inlineStr">
         <is>
@@ -23781,7 +24864,7 @@
       <c r="K445" s="7" t="inlineStr"/>
       <c r="L445" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M445" s="7" t="inlineStr"/>
@@ -23835,7 +24918,7 @@
       <c r="K446" s="7" t="inlineStr"/>
       <c r="L446" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049051704[해외 공용 품번], A1697663606[해외 공용 품번], A2049052304[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M446" s="7" t="inlineStr"/>
@@ -24280,14 +25363,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I455" s="7" t="inlineStr"/>
+      <c r="I455" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J455" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K455" s="7" t="inlineStr"/>
-      <c r="L455" s="7" t="inlineStr"/>
+      <c r="L455" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M455" s="7" t="inlineStr"/>
       <c r="N455" s="7" t="inlineStr">
         <is>
@@ -24330,14 +25421,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I456" s="7" t="inlineStr"/>
+      <c r="I456" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J456" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K456" s="7" t="inlineStr"/>
-      <c r="L456" s="7" t="inlineStr"/>
+      <c r="L456" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M456" s="7" t="inlineStr"/>
       <c r="N456" s="7" t="inlineStr">
         <is>
@@ -24380,14 +25479,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I457" s="7" t="inlineStr"/>
+      <c r="I457" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J457" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K457" s="7" t="inlineStr"/>
-      <c r="L457" s="7" t="inlineStr"/>
+      <c r="L457" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M457" s="7" t="inlineStr"/>
       <c r="N457" s="7" t="inlineStr">
         <is>
@@ -24430,14 +25537,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I458" s="7" t="inlineStr"/>
+      <c r="I458" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J458" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K458" s="7" t="inlineStr"/>
-      <c r="L458" s="7" t="inlineStr"/>
+      <c r="L458" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M458" s="7" t="inlineStr"/>
       <c r="N458" s="7" t="inlineStr">
         <is>
@@ -24480,14 +25595,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I459" s="7" t="n"/>
+      <c r="I459" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J459" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K459" s="7" t="n"/>
-      <c r="L459" s="7" t="n"/>
+      <c r="L459" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M459" s="7" t="n"/>
       <c r="N459" s="7" t="inlineStr">
         <is>
@@ -24530,14 +25653,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I460" s="7" t="n"/>
+      <c r="I460" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J460" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
         </is>
       </c>
       <c r="K460" s="7" t="n"/>
-      <c r="L460" s="7" t="n"/>
+      <c r="L460" s="7" t="inlineStr">
+        <is>
+          <t>A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M460" s="7" t="n"/>
       <c r="N460" s="7" t="inlineStr">
         <is>
@@ -24580,7 +25711,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I461" s="7" t="inlineStr"/>
+      <c r="I461" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J461" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -24589,7 +25724,7 @@
       <c r="K461" s="7" t="inlineStr"/>
       <c r="L461" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M461" s="7" t="inlineStr"/>
@@ -24634,7 +25769,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I462" s="7" t="inlineStr"/>
+      <c r="I462" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J462" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -24643,7 +25782,7 @@
       <c r="K462" s="7" t="inlineStr"/>
       <c r="L462" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M462" s="7" t="inlineStr"/>
@@ -24688,7 +25827,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I463" s="7" t="inlineStr"/>
+      <c r="I463" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J463" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -24697,7 +25840,7 @@
       <c r="K463" s="7" t="inlineStr"/>
       <c r="L463" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M463" s="7" t="inlineStr"/>
@@ -24742,7 +25885,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I464" s="7" t="inlineStr"/>
+      <c r="I464" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J464" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -24751,7 +25898,7 @@
       <c r="K464" s="7" t="inlineStr"/>
       <c r="L464" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M464" s="7" t="inlineStr"/>
@@ -24796,7 +25943,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I465" s="7" t="inlineStr"/>
+      <c r="I465" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J465" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -24805,7 +25956,7 @@
       <c r="K465" s="7" t="inlineStr"/>
       <c r="L465" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2049050804[해외 공용 품번], A2319054300[해외 공용 품번], A2049055902[키리스고, 해외 공용 품번], A2229055008[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M465" s="7" t="inlineStr"/>
@@ -24850,7 +26001,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I466" s="7" t="inlineStr"/>
+      <c r="I466" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J466" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -24859,7 +26014,7 @@
       <c r="K466" s="7" t="inlineStr"/>
       <c r="L466" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M466" s="7" t="inlineStr"/>
@@ -24904,7 +26059,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I467" s="7" t="inlineStr"/>
+      <c r="I467" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J467" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -24913,7 +26072,7 @@
       <c r="K467" s="7" t="inlineStr"/>
       <c r="L467" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M467" s="7" t="inlineStr"/>
@@ -24958,7 +26117,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I468" s="7" t="inlineStr"/>
+      <c r="I468" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J468" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -24967,7 +26130,7 @@
       <c r="K468" s="7" t="inlineStr"/>
       <c r="L468" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M468" s="7" t="inlineStr"/>
@@ -25012,7 +26175,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I469" s="7" t="inlineStr"/>
+      <c r="I469" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J469" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25021,7 +26188,7 @@
       <c r="K469" s="7" t="inlineStr"/>
       <c r="L469" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M469" s="7" t="inlineStr"/>
@@ -25066,7 +26233,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I470" s="7" t="inlineStr"/>
+      <c r="I470" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J470" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25075,7 +26246,7 @@
       <c r="K470" s="7" t="inlineStr"/>
       <c r="L470" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M470" s="7" t="inlineStr"/>
@@ -25120,7 +26291,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I471" s="7" t="inlineStr"/>
+      <c r="I471" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J471" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25129,7 +26304,7 @@
       <c r="K471" s="7" t="inlineStr"/>
       <c r="L471" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M471" s="7" t="inlineStr"/>
@@ -25174,7 +26349,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I472" s="7" t="inlineStr"/>
+      <c r="I472" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J472" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25183,7 +26362,7 @@
       <c r="K472" s="7" t="inlineStr"/>
       <c r="L472" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M472" s="7" t="inlineStr"/>
@@ -25228,7 +26407,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I473" s="7" t="inlineStr"/>
+      <c r="I473" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J473" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25237,7 +26420,7 @@
       <c r="K473" s="7" t="inlineStr"/>
       <c r="L473" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M473" s="7" t="inlineStr"/>
@@ -25282,7 +26465,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I474" s="7" t="inlineStr"/>
+      <c r="I474" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J474" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25291,7 +26478,7 @@
       <c r="K474" s="7" t="inlineStr"/>
       <c r="L474" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M474" s="7" t="inlineStr"/>
@@ -25336,7 +26523,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I475" s="7" t="inlineStr"/>
+      <c r="I475" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J475" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25345,7 +26536,7 @@
       <c r="K475" s="7" t="inlineStr"/>
       <c r="L475" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2319054300[해외 공용 품번], A2059050600[해외 공용 품번], A2319050639[키리스고, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M475" s="7" t="inlineStr"/>
@@ -25640,7 +26831,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I481" s="7" t="inlineStr"/>
+      <c r="I481" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J481" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25649,7 +26844,7 @@
       <c r="K481" s="7" t="inlineStr"/>
       <c r="L481" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229055008[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M481" s="7" t="inlineStr"/>
@@ -25694,7 +26889,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I482" s="7" t="inlineStr"/>
+      <c r="I482" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J482" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25703,7 +26902,7 @@
       <c r="K482" s="7" t="inlineStr"/>
       <c r="L482" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229055008[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M482" s="7" t="inlineStr"/>
@@ -25748,7 +26947,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I483" s="7" t="inlineStr"/>
+      <c r="I483" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J483" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25757,7 +26960,7 @@
       <c r="K483" s="7" t="inlineStr"/>
       <c r="L483" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229055008[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M483" s="7" t="inlineStr"/>
@@ -25802,7 +27005,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I484" s="7" t="inlineStr"/>
+      <c r="I484" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J484" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25811,7 +27018,7 @@
       <c r="K484" s="7" t="inlineStr"/>
       <c r="L484" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229055008[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M484" s="7" t="inlineStr"/>
@@ -25856,7 +27063,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I485" s="7" t="inlineStr"/>
+      <c r="I485" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J485" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25865,7 +27076,7 @@
       <c r="K485" s="7" t="inlineStr"/>
       <c r="L485" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229055008[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M485" s="7" t="inlineStr"/>
@@ -25910,7 +27121,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I486" s="7" t="inlineStr"/>
+      <c r="I486" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J486" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25919,7 +27134,7 @@
       <c r="K486" s="7" t="inlineStr"/>
       <c r="L486" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229055008[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M486" s="7" t="inlineStr"/>
@@ -25964,7 +27179,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I487" s="7" t="inlineStr"/>
+      <c r="I487" s="7" t="inlineStr">
+        <is>
+          <t>A2127601906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J487" s="7" t="inlineStr">
         <is>
           <t>HU64</t>
@@ -25973,7 +27192,7 @@
       <c r="K487" s="7" t="inlineStr"/>
       <c r="L487" s="7" t="inlineStr">
         <is>
-          <t>FCC IYZDC12B[3버튼]</t>
+          <t>FCC IYZDC12B[3버튼], A2229055008[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M487" s="7" t="inlineStr"/>
@@ -27949,359 +29168,366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr"/>
+      <c r="A2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 같고, 칩코드 뒤에 '키종류'를 추가했습니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(G클래스 구형은 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 벤츠는 EIS(EZS)에 꽂는 크롬키·키리스고 키 모두 '스마트키'로 적었고, 폴딩키·카드키는 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433MHz)만 적었습니다. 미국(315MHz) 사양 키(FCC IYZ3312·NBGDM3 등)는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2019(단종)' 형식입니다. 원본 목록 연식을 그대로 따랐습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">- 벤츠 키는 ID46 같은 일반 트랜스폰더가 아니라 NEC 프로세서 키(FBS3/FBS4)라서 'XT27A/A66·XT27B·XT57B 호환' 칸은 비어 있습니다(기아 파일 규칙상 해당 칩 없음). </t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>- 이모빌라이저는 EIS(EZS, 전자식 점화 스위치 모듈)입니다. FBS3/FBS4 세대는 칩코드 칸에 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>- 키블레이드(키웨이)는 비상키 블레이드 HU64입니다(1997~2014 인서트 및 2019+ FBS4 비상키 모두 HU64 표기). 키블레이드 부품번호는 찾지 못해 비웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>- 출처 칸은 검색에서 근거로 쓴 페이지입니다. 원문은 이 환경에서 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr"/>
+      <c r="A14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>- 주황색: 추정이거나 자료가 서로 다른 값, 또는 해당 연식 검색 자료가 없어 이전 연식 기준으로 채운 값 — 실물 키/VIN(SA코드 803/804 = FBS4)으로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>- 전환 연식(FBS3→FBS4)은 색 없이 칩코드·이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: FBS3[2013.4 이전 생산], FBS4[2013.4 이후 생산]).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
+      <c r="A18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>- 모델마다 연식별로 검색했고 연식별 검색 기록은 research/benz/yearly.md에 있습니다. 같은 세대 안에서도 FBS3→FBS4 전환, 페이스리프트 후 신형 키 디자인, 키리스고 옵션 여부가 달라집니다.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>- 신형 키 디자인: E클래스 W213 2017~, S클래스 2018 페이스리프트~, G클래스 2019~, A·C·CLA·CLS·GLB·GLC·GLS 2020~(Gen3), GLE W167 2019~(티어드롭), 2021~ W223·W206·W214·X254·EQS/EQE는 MS5 계열 신형 키. 구형 키와 호환 안 됨.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>- 확인된 국내 사양(433/434MHz) 순정 품번: W205 A2059053609(3버튼)·A2059050000/A2059050600(2버튼), W222·C217·X222 A2229059610, W177 A1779057902, EQA·EQB A1779054606, FBS4 공용 보드 IYZDC12B.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>- FBS4 적용 시점: W212 2013.4~, 166(ML·GL)·207(E쿠페/카브리올레)·V212 2013.7~, 218(CLS) 2014.9~, 117(CLA)·156(GLA) 2014.11~, 172(SLK) 2015.4~, 205·217·222·231은 처음부터 FBS4. A클래스 W176은 2014년부터 FBS4.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>- FBS3 키는 로컬 장비(NEC/BGA 등)로 키 제작이 가능하지만, FBS4는 독일 벤츠 서버 인증이 필요해 사실상 딜러(또는 XENTRY 계정 보유 업체) 작업입니다.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>- 2021년 이후 신형(W206·W223·W214·X254·EQS/EQE 등)도 FBS4 딜러 전용으로 분류됩니다. 비상키는 Gen4 인서트(HU64).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>- FBS3/FBS4 키 구분: 키 기판 번호 문자열에 'K'가 앞에 있으면 FBS3 풀 스마트키, 중간에 있으면 FBS4 풀 스마트키. FBS4 기판에는 오른쪽에 트랜지스터가 있고 칩이 더 작습니다.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>- 순정 FBS4 스마트키(433MHz, 3버튼) IYZDC12B는 2014-2023년식 적용 표기, W222 S클래스 FBS4 키리스고 키 A2229059610(433MHz).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>- G클래스(W463) 구형: 2000~2001년식 키 자료 상충, 2002~2005년식 IR 스마트키·트랜스폰더 막대키 병존, 2006년식 검정 키, 2007년형부터 크롬 키, 2016년식 FBS3/FBS4 자료 상충.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="n"/>
+      <c r="A29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="n"/>
+      <c r="A37" s="14" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="n"/>
+      <c r="A46" s="14" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="n"/>
+      <c r="A50" s="14" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>- W246 FBS4는 2014.11 생산부터(EASYGUARD·abkeys W246 FBS4 EZS 2469057503) — 같은 MFA 플랫폼 W176·A45·CLA·GLA도 2014.11 전환으로 정리</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>- G클래스 W463 2002~: EIS(EZS) + 적외선 키(FBS3)로 바뀜(fixautosmart "G500 2002-2014 W463 EIS", CGDI MB G클래스 2003~ 적외선 모드) — 트랜스폰더 막대키는 2001년까지 DAS 차량</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>- 벤츠 순정 부품번호(공란 행 보완, auto-keys.eu OEM 키 433/434MHz): W204 A2049051704(2버튼, FBS3)·A2049055702(3버튼), W213 A2139059209·A2139056509(AMG), W206 A2239058707, W223 A2239057507·A2239054408(AMG), W167 A1679054203 — 315MHz 번호(A1679054503 등) 제외, 한국 사양 번호 미확인이라 [해외 공용 품번]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>- 벤츠 EPC(catcar.info Car-Europe·Cross-country vehicle-Europe 카탈로그) FRONT DOORS &gt; CLOSING SYSTEM의 KEY(전자 키)·MASTER KEY(비상 기계식 키) 현행 번호: 국가 코드 494(미국)·460(캐나다)·498(일본)·762·763(315MHz 리모컨)과 택시 등 특수 옵션 코드가 붙은 번호, 다른 번호로 대체(Replaced by)된 구 번호는 제외. 889(KEYLESS-GO) 조건 번호는 [키리스고], B66·B67·B68 키 디자인 옵션은 [옵션 B66] 등으로 표기, 적용 시작·종료 날짜(From·To Date)가 있으면 연식에 반영. 한국 사양(유럽형 433MHz) 적용 여부는 EPC에 따로 표시되지 않아 [해외 공용 품번]. 2019년 이후 신형(W214·X254·H247·X247·X167·C257·R232·EQ 계열 등)은 카탈로그 범위 밖이라 미기재</t>
         </is>
       </c>
     </row>

--- a/벤츠_models.xlsx
+++ b/벤츠_models.xlsx
@@ -88,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -3008,7 +3011,11 @@
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="n"/>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M44" s="7" t="inlineStr"/>
       <c r="N44" s="7" t="inlineStr">
         <is>
@@ -3017,7 +3024,7 @@
       </c>
       <c r="O44" s="7" t="inlineStr">
         <is>
-          <t>carkeyhelper(C118 스마트키)</t>
+          <t>carkeyhelper(C118 스마트키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr"/>
@@ -3058,7 +3065,11 @@
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="n"/>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="7" t="inlineStr">
         <is>
@@ -3067,7 +3078,7 @@
       </c>
       <c r="O45" s="7" t="inlineStr">
         <is>
-          <t>carkeyhelper(C118)</t>
+          <t>carkeyhelper(C118), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr"/>
@@ -3108,7 +3119,11 @@
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
-      <c r="L46" s="7" t="n"/>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="7" t="inlineStr">
         <is>
@@ -3117,7 +3132,7 @@
       </c>
       <c r="O46" s="7" t="inlineStr">
         <is>
-          <t>ebay(2022 CLA250 C118 키), autokeystore(FBS4 433MHz 3버튼 HU64)</t>
+          <t>ebay(2022 CLA250 C118 키), autokeystore(FBS4 433MHz 3버튼 HU64), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr"/>
@@ -3158,7 +3173,11 @@
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr"/>
-      <c r="L47" s="7" t="n"/>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr">
         <is>
@@ -3167,7 +3186,7 @@
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
-          <t>autokeystore, carkeyhelper</t>
+          <t>autokeystore, carkeyhelper, auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P47" s="7" t="inlineStr"/>
@@ -3208,7 +3227,11 @@
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
-      <c r="L48" s="7" t="n"/>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M48" s="7" t="inlineStr"/>
       <c r="N48" s="7" t="inlineStr">
         <is>
@@ -3217,7 +3240,7 @@
       </c>
       <c r="O48" s="7" t="inlineStr">
         <is>
-          <t>auto-data(C118 FL 2023), carkeyhelper</t>
+          <t>auto-data(C118 FL 2023), carkeyhelper, auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr"/>
@@ -3258,7 +3281,11 @@
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="n"/>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="7" t="inlineStr">
         <is>
@@ -3267,7 +3294,7 @@
       </c>
       <c r="O49" s="7" t="inlineStr">
         <is>
-          <t>carkeyhelper(C118 2019-2025)</t>
+          <t>carkeyhelper(C118 2019-2025), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P49" s="7" t="inlineStr"/>
@@ -3714,7 +3741,11 @@
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr"/>
-      <c r="L57" s="7" t="n"/>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="7" t="inlineStr">
         <is>
@@ -3723,7 +3754,7 @@
       </c>
       <c r="O57" s="7" t="inlineStr">
         <is>
-          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
+          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P57" s="7" t="inlineStr"/>
@@ -3764,7 +3795,11 @@
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr"/>
-      <c r="L58" s="7" t="n"/>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M58" s="7" t="inlineStr"/>
       <c r="N58" s="7" t="inlineStr">
         <is>
@@ -3773,7 +3808,7 @@
       </c>
       <c r="O58" s="7" t="inlineStr">
         <is>
-          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
+          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr"/>
@@ -3814,7 +3849,11 @@
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr"/>
-      <c r="L59" s="7" t="n"/>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M59" s="7" t="inlineStr"/>
       <c r="N59" s="7" t="inlineStr">
         <is>
@@ -3823,7 +3862,7 @@
       </c>
       <c r="O59" s="7" t="inlineStr">
         <is>
-          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
+          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P59" s="7" t="inlineStr"/>
@@ -3864,7 +3903,11 @@
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="n"/>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="10" t="inlineStr">
         <is>
@@ -3873,7 +3916,7 @@
       </c>
       <c r="O60" s="7" t="inlineStr">
         <is>
-          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
+          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P60" s="10" t="n"/>
@@ -3914,7 +3957,11 @@
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr"/>
-      <c r="L61" s="7" t="n"/>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="10" t="inlineStr">
         <is>
@@ -3923,7 +3970,7 @@
       </c>
       <c r="O61" s="7" t="inlineStr">
         <is>
-          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
+          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P61" s="10" t="n"/>
@@ -3964,7 +4011,11 @@
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="n"/>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="10" t="inlineStr">
         <is>
@@ -3973,7 +4024,7 @@
       </c>
       <c r="O62" s="7" t="inlineStr">
         <is>
-          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
+          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P62" s="10" t="n"/>
@@ -4014,7 +4065,11 @@
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr"/>
-      <c r="L63" s="7" t="n"/>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="10" t="inlineStr">
         <is>
@@ -4023,7 +4078,7 @@
       </c>
       <c r="O63" s="7" t="inlineStr">
         <is>
-          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키)</t>
+          <t>mbpartsgiant·fcpeuro(CLA45 S C118 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P63" s="10" t="n"/>
@@ -6602,7 +6657,11 @@
         </is>
       </c>
       <c r="K111" s="7" t="inlineStr"/>
-      <c r="L111" s="7" t="n"/>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M111" s="7" t="inlineStr"/>
       <c r="N111" s="7" t="inlineStr">
         <is>
@@ -6611,7 +6670,7 @@
       </c>
       <c r="O111" s="7" t="inlineStr">
         <is>
-          <t>wikipedia(CLE 2023.10 생산), mbworld(CLE digital key)</t>
+          <t>wikipedia(CLE 2023.10 생산), mbworld(CLE digital key), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P111" s="7" t="inlineStr"/>
@@ -6652,7 +6711,11 @@
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr"/>
-      <c r="L112" s="7" t="n"/>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M112" s="7" t="inlineStr"/>
       <c r="N112" s="7" t="inlineStr">
         <is>
@@ -6661,7 +6724,7 @@
       </c>
       <c r="O112" s="7" t="inlineStr">
         <is>
-          <t>mbusa(CLE 2025-10 디지털 차키)</t>
+          <t>mbusa(CLE 2025-10 디지털 차키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P112" s="7" t="inlineStr"/>
@@ -6702,7 +6765,11 @@
         </is>
       </c>
       <c r="K113" s="7" t="inlineStr"/>
-      <c r="L113" s="7" t="n"/>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M113" s="7" t="inlineStr"/>
       <c r="N113" s="7" t="inlineStr">
         <is>
@@ -6711,7 +6778,7 @@
       </c>
       <c r="O113" s="7" t="inlineStr">
         <is>
-          <t>mbusa(CLE 2026-06 디지털 차키)</t>
+          <t>mbusa(CLE 2026-06 디지털 차키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P113" s="7" t="inlineStr"/>
@@ -8224,7 +8291,11 @@
         </is>
       </c>
       <c r="K140" s="7" t="inlineStr"/>
-      <c r="L140" s="7" t="n"/>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M140" s="7" t="inlineStr"/>
       <c r="N140" s="7" t="inlineStr">
         <is>
@@ -8233,7 +8304,7 @@
       </c>
       <c r="O140" s="7" t="inlineStr">
         <is>
-          <t>mbworld(W214 신형 키 비상키 분리 버튼), mbusa(W214 2024 디지털 차키)</t>
+          <t>mbworld(W214 신형 키 비상키 분리 버튼), mbusa(W214 2024 디지털 차키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P140" s="7" t="inlineStr"/>
@@ -8274,7 +8345,11 @@
         </is>
       </c>
       <c r="K141" s="7" t="inlineStr"/>
-      <c r="L141" s="7" t="n"/>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M141" s="7" t="inlineStr"/>
       <c r="N141" s="7" t="inlineStr">
         <is>
@@ -8283,7 +8358,7 @@
       </c>
       <c r="O141" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(2026 키 호환 — VIN 확인)</t>
+          <t>carinterior.alibaba(2026 키 호환 — VIN 확인), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P141" s="7" t="inlineStr"/>
@@ -8324,7 +8399,11 @@
         </is>
       </c>
       <c r="K142" s="7" t="inlineStr"/>
-      <c r="L142" s="7" t="n"/>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M142" s="7" t="inlineStr"/>
       <c r="N142" s="7" t="inlineStr">
         <is>
@@ -8333,7 +8412,7 @@
       </c>
       <c r="O142" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(2026 키 호환)</t>
+          <t>carinterior.alibaba(2026 키 호환), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P142" s="7" t="inlineStr"/>
@@ -10552,7 +10631,11 @@
         </is>
       </c>
       <c r="K182" s="7" t="inlineStr"/>
-      <c r="L182" s="7" t="n"/>
+      <c r="L182" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M182" s="7" t="inlineStr"/>
       <c r="N182" s="7" t="inlineStr">
         <is>
@@ -10561,7 +10644,7 @@
       </c>
       <c r="O182" s="7" t="inlineStr">
         <is>
-          <t>mbworld(2025 E53 키-프로필 연동), autoevolution(E53 W214)</t>
+          <t>mbworld(2025 E53 키-프로필 연동), autoevolution(E53 W214), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P182" s="7" t="inlineStr"/>
@@ -10602,7 +10685,11 @@
         </is>
       </c>
       <c r="K183" s="7" t="inlineStr"/>
-      <c r="L183" s="7" t="n"/>
+      <c r="L183" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M183" s="7" t="inlineStr"/>
       <c r="N183" s="7" t="inlineStr">
         <is>
@@ -10611,7 +10698,7 @@
       </c>
       <c r="O183" s="7" t="inlineStr">
         <is>
-          <t>mbworld(2025 E53 키-프로필 연동), autoevolution(E53 W214)</t>
+          <t>mbworld(2025 E53 키-프로필 연동), autoevolution(E53 W214), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P183" s="7" t="inlineStr"/>
@@ -10652,7 +10739,11 @@
         </is>
       </c>
       <c r="K184" s="7" t="inlineStr"/>
-      <c r="L184" s="7" t="n"/>
+      <c r="L184" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M184" s="7" t="inlineStr"/>
       <c r="N184" s="10" t="inlineStr">
         <is>
@@ -10661,7 +10752,7 @@
       </c>
       <c r="O184" s="7" t="inlineStr">
         <is>
-          <t>mbworld(2025 E53 키-프로필 연동), autoevolution(E53 W214)</t>
+          <t>mbworld(2025 E53 키-프로필 연동), autoevolution(E53 W214), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P184" s="10" t="n"/>
@@ -14798,7 +14889,11 @@
         </is>
       </c>
       <c r="K259" s="7" t="inlineStr"/>
-      <c r="L259" s="7" t="n"/>
+      <c r="L259" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M259" s="7" t="inlineStr"/>
       <c r="N259" s="7" t="inlineStr">
         <is>
@@ -14807,7 +14902,7 @@
       </c>
       <c r="O259" s="7" t="inlineStr">
         <is>
-          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이)</t>
+          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P259" s="7" t="inlineStr"/>
@@ -14848,7 +14943,11 @@
         </is>
       </c>
       <c r="K260" s="7" t="inlineStr"/>
-      <c r="L260" s="7" t="n"/>
+      <c r="L260" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M260" s="7" t="inlineStr"/>
       <c r="N260" s="7" t="inlineStr">
         <is>
@@ -14857,7 +14956,7 @@
       </c>
       <c r="O260" s="7" t="inlineStr">
         <is>
-          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이)</t>
+          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P260" s="7" t="inlineStr"/>
@@ -14898,7 +14997,11 @@
         </is>
       </c>
       <c r="K261" s="7" t="inlineStr"/>
-      <c r="L261" s="7" t="n"/>
+      <c r="L261" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M261" s="7" t="inlineStr"/>
       <c r="N261" s="7" t="inlineStr">
         <is>
@@ -14907,7 +15010,7 @@
       </c>
       <c r="O261" s="7" t="inlineStr">
         <is>
-          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이)</t>
+          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P261" s="7" t="inlineStr"/>
@@ -14948,7 +15051,11 @@
         </is>
       </c>
       <c r="K262" s="7" t="inlineStr"/>
-      <c r="L262" s="7" t="n"/>
+      <c r="L262" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M262" s="7" t="inlineStr"/>
       <c r="N262" s="7" t="inlineStr">
         <is>
@@ -14957,7 +15064,7 @@
       </c>
       <c r="O262" s="7" t="inlineStr">
         <is>
-          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이)</t>
+          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P262" s="7" t="inlineStr"/>
@@ -14998,7 +15105,11 @@
         </is>
       </c>
       <c r="K263" s="7" t="inlineStr"/>
-      <c r="L263" s="7" t="n"/>
+      <c r="L263" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M263" s="7" t="inlineStr"/>
       <c r="N263" s="7" t="inlineStr">
         <is>
@@ -15007,7 +15118,7 @@
       </c>
       <c r="O263" s="7" t="inlineStr">
         <is>
-          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이)</t>
+          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P263" s="7" t="inlineStr"/>
@@ -15048,7 +15159,11 @@
         </is>
       </c>
       <c r="K264" s="7" t="inlineStr"/>
-      <c r="L264" s="7" t="n"/>
+      <c r="L264" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M264" s="7" t="inlineStr"/>
       <c r="N264" s="7" t="inlineStr">
         <is>
@@ -15057,7 +15172,7 @@
       </c>
       <c r="O264" s="7" t="inlineStr">
         <is>
-          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이)</t>
+          <t>encycarpedia(Z223 2021-2026), carinterior.alibaba(마이바흐 키 — 세대·생산연도별 상이), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P264" s="7" t="inlineStr"/>
@@ -16210,7 +16325,11 @@
         </is>
       </c>
       <c r="K285" s="7" t="inlineStr"/>
-      <c r="L285" s="7" t="n"/>
+      <c r="L285" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M285" s="7" t="inlineStr"/>
       <c r="N285" s="7" t="inlineStr">
         <is>
@@ -16219,7 +16338,7 @@
       </c>
       <c r="O285" s="7" t="inlineStr">
         <is>
-          <t>justanswer(2021 GLA250 key fob), mbworld(H247 key replacement)</t>
+          <t>justanswer(2021 GLA250 key fob), mbworld(H247 key replacement), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P285" s="7" t="inlineStr"/>
@@ -16260,7 +16379,11 @@
         </is>
       </c>
       <c r="K286" s="7" t="inlineStr"/>
-      <c r="L286" s="7" t="n"/>
+      <c r="L286" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M286" s="7" t="inlineStr"/>
       <c r="N286" s="7" t="inlineStr">
         <is>
@@ -16269,7 +16392,7 @@
       </c>
       <c r="O286" s="7" t="inlineStr">
         <is>
-          <t>justanswer(2021 GLA250 key fob), mbworld(H247 key replacement)</t>
+          <t>justanswer(2021 GLA250 key fob), mbworld(H247 key replacement), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P286" s="7" t="inlineStr"/>
@@ -16310,7 +16433,11 @@
         </is>
       </c>
       <c r="K287" s="7" t="inlineStr"/>
-      <c r="L287" s="7" t="n"/>
+      <c r="L287" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M287" s="7" t="inlineStr"/>
       <c r="N287" s="7" t="inlineStr">
         <is>
@@ -16319,7 +16446,7 @@
       </c>
       <c r="O287" s="7" t="inlineStr">
         <is>
-          <t>justanswer(2021 GLA250 key fob), mbworld(H247 key replacement)</t>
+          <t>justanswer(2021 GLA250 key fob), mbworld(H247 key replacement), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P287" s="7" t="inlineStr"/>
@@ -16360,7 +16487,11 @@
         </is>
       </c>
       <c r="K288" s="7" t="inlineStr"/>
-      <c r="L288" s="7" t="n"/>
+      <c r="L288" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M288" s="7" t="inlineStr"/>
       <c r="N288" s="7" t="inlineStr">
         <is>
@@ -16369,7 +16500,7 @@
       </c>
       <c r="O288" s="7" t="inlineStr">
         <is>
-          <t>auto-data(H247 FL 2023), mbworld</t>
+          <t>auto-data(H247 FL 2023), mbworld, auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P288" s="7" t="inlineStr"/>
@@ -16410,7 +16541,11 @@
         </is>
       </c>
       <c r="K289" s="7" t="inlineStr"/>
-      <c r="L289" s="7" t="n"/>
+      <c r="L289" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M289" s="7" t="inlineStr"/>
       <c r="N289" s="7" t="inlineStr">
         <is>
@@ -16419,7 +16554,7 @@
       </c>
       <c r="O289" s="7" t="inlineStr">
         <is>
-          <t>auto-data(H247 FL 2023), mbworld</t>
+          <t>auto-data(H247 FL 2023), mbworld, auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P289" s="7" t="inlineStr"/>
@@ -16460,7 +16595,11 @@
         </is>
       </c>
       <c r="K290" s="7" t="inlineStr"/>
-      <c r="L290" s="7" t="n"/>
+      <c r="L290" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M290" s="7" t="inlineStr"/>
       <c r="N290" s="7" t="inlineStr">
         <is>
@@ -16469,7 +16608,7 @@
       </c>
       <c r="O290" s="7" t="inlineStr">
         <is>
-          <t>auto-data(H247 FL 2023), mbworld</t>
+          <t>auto-data(H247 FL 2023), mbworld, auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P290" s="7" t="inlineStr"/>
@@ -16510,7 +16649,11 @@
         </is>
       </c>
       <c r="K291" s="7" t="inlineStr"/>
-      <c r="L291" s="7" t="n"/>
+      <c r="L291" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M291" s="7" t="inlineStr"/>
       <c r="N291" s="10" t="inlineStr">
         <is>
@@ -16519,7 +16662,7 @@
       </c>
       <c r="O291" s="7" t="inlineStr">
         <is>
-          <t>auto-data(H247 FL 2023), mbworld</t>
+          <t>auto-data(H247 FL 2023), mbworld, auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P291" s="10" t="n"/>
@@ -17024,7 +17167,11 @@
         </is>
       </c>
       <c r="K300" s="7" t="inlineStr"/>
-      <c r="L300" s="7" t="n"/>
+      <c r="L300" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M300" s="7" t="inlineStr"/>
       <c r="N300" s="7" t="inlineStr">
         <is>
@@ -17033,7 +17180,7 @@
       </c>
       <c r="O300" s="7" t="inlineStr">
         <is>
-          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35)</t>
+          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P300" s="7" t="inlineStr"/>
@@ -17074,7 +17221,11 @@
         </is>
       </c>
       <c r="K301" s="7" t="inlineStr"/>
-      <c r="L301" s="7" t="n"/>
+      <c r="L301" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M301" s="7" t="inlineStr"/>
       <c r="N301" s="7" t="inlineStr">
         <is>
@@ -17083,7 +17234,7 @@
       </c>
       <c r="O301" s="7" t="inlineStr">
         <is>
-          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35)</t>
+          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P301" s="7" t="inlineStr"/>
@@ -17124,7 +17275,11 @@
         </is>
       </c>
       <c r="K302" s="7" t="inlineStr"/>
-      <c r="L302" s="7" t="n"/>
+      <c r="L302" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M302" s="7" t="inlineStr"/>
       <c r="N302" s="7" t="inlineStr">
         <is>
@@ -17133,7 +17288,7 @@
       </c>
       <c r="O302" s="7" t="inlineStr">
         <is>
-          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35)</t>
+          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P302" s="7" t="inlineStr"/>
@@ -17174,7 +17329,11 @@
         </is>
       </c>
       <c r="K303" s="7" t="inlineStr"/>
-      <c r="L303" s="7" t="n"/>
+      <c r="L303" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M303" s="7" t="inlineStr"/>
       <c r="N303" s="10" t="inlineStr">
         <is>
@@ -17183,7 +17342,7 @@
       </c>
       <c r="O303" s="7" t="inlineStr">
         <is>
-          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35)</t>
+          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P303" s="10" t="n"/>
@@ -17224,7 +17383,11 @@
         </is>
       </c>
       <c r="K304" s="7" t="inlineStr"/>
-      <c r="L304" s="7" t="n"/>
+      <c r="L304" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M304" s="7" t="inlineStr"/>
       <c r="N304" s="10" t="inlineStr">
         <is>
@@ -17233,7 +17396,7 @@
       </c>
       <c r="O304" s="7" t="inlineStr">
         <is>
-          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35)</t>
+          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P304" s="10" t="n"/>
@@ -17274,7 +17437,11 @@
         </is>
       </c>
       <c r="K305" s="7" t="inlineStr"/>
-      <c r="L305" s="7" t="n"/>
+      <c r="L305" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M305" s="7" t="inlineStr"/>
       <c r="N305" s="10" t="inlineStr">
         <is>
@@ -17283,7 +17450,7 @@
       </c>
       <c r="O305" s="7" t="inlineStr">
         <is>
-          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35)</t>
+          <t>amazon(KKNCO 2021-2024 GLA45·GLA35 키 배터리 적용표), mbworld(GLA45/35), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P305" s="10" t="n"/>
@@ -17324,7 +17491,11 @@
         </is>
       </c>
       <c r="K306" s="7" t="inlineStr"/>
-      <c r="L306" s="7" t="n"/>
+      <c r="L306" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M306" s="7" t="inlineStr"/>
       <c r="N306" s="7" t="inlineStr">
         <is>
@@ -17333,7 +17504,7 @@
       </c>
       <c r="O306" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2025 GLB250 순정 키), mbworld(GLB remote start fob)</t>
+          <t>ebay(2020-2025 GLB250 순정 키), mbworld(GLB remote start fob), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P306" s="7" t="inlineStr"/>
@@ -17374,7 +17545,11 @@
         </is>
       </c>
       <c r="K307" s="7" t="inlineStr"/>
-      <c r="L307" s="7" t="n"/>
+      <c r="L307" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M307" s="7" t="inlineStr"/>
       <c r="N307" s="7" t="inlineStr">
         <is>
@@ -17383,7 +17558,7 @@
       </c>
       <c r="O307" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2025 GLB250 순정 키), mbworld(GLB remote start fob)</t>
+          <t>ebay(2020-2025 GLB250 순정 키), mbworld(GLB remote start fob), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P307" s="7" t="inlineStr"/>
@@ -17424,7 +17599,11 @@
         </is>
       </c>
       <c r="K308" s="7" t="inlineStr"/>
-      <c r="L308" s="7" t="n"/>
+      <c r="L308" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M308" s="7" t="inlineStr"/>
       <c r="N308" s="7" t="inlineStr">
         <is>
@@ -17433,7 +17612,7 @@
       </c>
       <c r="O308" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2025 GLB250 순정 키), mbworld(GLB remote start fob)</t>
+          <t>ebay(2020-2025 GLB250 순정 키), mbworld(GLB remote start fob), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P308" s="7" t="inlineStr"/>
@@ -17474,7 +17653,11 @@
         </is>
       </c>
       <c r="K309" s="7" t="inlineStr"/>
-      <c r="L309" s="7" t="n"/>
+      <c r="L309" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M309" s="7" t="inlineStr"/>
       <c r="N309" s="7" t="inlineStr">
         <is>
@@ -17483,7 +17666,7 @@
       </c>
       <c r="O309" s="7" t="inlineStr">
         <is>
-          <t>autoevolution(2024 GLB35 FL), mbusa(2023 GLB250 keyless)</t>
+          <t>autoevolution(2024 GLB35 FL), mbusa(2023 GLB250 keyless), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P309" s="7" t="inlineStr"/>
@@ -17524,7 +17707,11 @@
         </is>
       </c>
       <c r="K310" s="7" t="inlineStr"/>
-      <c r="L310" s="7" t="n"/>
+      <c r="L310" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M310" s="7" t="inlineStr"/>
       <c r="N310" s="7" t="inlineStr">
         <is>
@@ -17533,7 +17720,7 @@
       </c>
       <c r="O310" s="7" t="inlineStr">
         <is>
-          <t>autoevolution(2024 GLB35 FL), mbusa(2023 GLB250 keyless)</t>
+          <t>autoevolution(2024 GLB35 FL), mbusa(2023 GLB250 keyless), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P310" s="7" t="inlineStr"/>
@@ -17574,7 +17761,11 @@
         </is>
       </c>
       <c r="K311" s="7" t="inlineStr"/>
-      <c r="L311" s="7" t="n"/>
+      <c r="L311" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M311" s="7" t="inlineStr"/>
       <c r="N311" s="7" t="inlineStr">
         <is>
@@ -17583,7 +17774,7 @@
       </c>
       <c r="O311" s="7" t="inlineStr">
         <is>
-          <t>autoevolution(2024 GLB35 FL), mbusa(2023 GLB250 keyless)</t>
+          <t>autoevolution(2024 GLB35 FL), mbusa(2023 GLB250 keyless), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P311" s="7" t="inlineStr"/>
@@ -17624,7 +17815,11 @@
         </is>
       </c>
       <c r="K312" s="7" t="inlineStr"/>
-      <c r="L312" s="7" t="n"/>
+      <c r="L312" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M312" s="7" t="inlineStr"/>
       <c r="N312" s="10" t="inlineStr">
         <is>
@@ -17633,7 +17828,7 @@
       </c>
       <c r="O312" s="7" t="inlineStr">
         <is>
-          <t>autoevolution(2024 GLB35 FL), mbusa(2023 GLB250 keyless)</t>
+          <t>autoevolution(2024 GLB35 FL), mbusa(2023 GLB250 keyless), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P312" s="10" t="n"/>
@@ -17674,7 +17869,11 @@
         </is>
       </c>
       <c r="K313" s="7" t="inlineStr"/>
-      <c r="L313" s="7" t="n"/>
+      <c r="L313" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M313" s="7" t="inlineStr"/>
       <c r="N313" s="7" t="inlineStr">
         <is>
@@ -17683,7 +17882,7 @@
       </c>
       <c r="O313" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL)</t>
+          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P313" s="7" t="inlineStr"/>
@@ -17724,7 +17923,11 @@
         </is>
       </c>
       <c r="K314" s="7" t="inlineStr"/>
-      <c r="L314" s="7" t="n"/>
+      <c r="L314" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M314" s="7" t="inlineStr"/>
       <c r="N314" s="7" t="inlineStr">
         <is>
@@ -17733,7 +17936,7 @@
       </c>
       <c r="O314" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL)</t>
+          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P314" s="7" t="inlineStr"/>
@@ -17774,7 +17977,11 @@
         </is>
       </c>
       <c r="K315" s="7" t="inlineStr"/>
-      <c r="L315" s="7" t="n"/>
+      <c r="L315" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M315" s="7" t="inlineStr"/>
       <c r="N315" s="7" t="inlineStr">
         <is>
@@ -17783,7 +17990,7 @@
       </c>
       <c r="O315" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL)</t>
+          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P315" s="7" t="inlineStr"/>
@@ -17824,7 +18031,11 @@
         </is>
       </c>
       <c r="K316" s="7" t="inlineStr"/>
-      <c r="L316" s="7" t="n"/>
+      <c r="L316" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M316" s="7" t="inlineStr"/>
       <c r="N316" s="7" t="inlineStr">
         <is>
@@ -17833,7 +18044,7 @@
       </c>
       <c r="O316" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL)</t>
+          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P316" s="7" t="inlineStr"/>
@@ -17874,7 +18085,11 @@
         </is>
       </c>
       <c r="K317" s="7" t="inlineStr"/>
-      <c r="L317" s="7" t="n"/>
+      <c r="L317" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M317" s="7" t="inlineStr"/>
       <c r="N317" s="7" t="inlineStr">
         <is>
@@ -17883,7 +18098,7 @@
       </c>
       <c r="O317" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL)</t>
+          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P317" s="7" t="inlineStr"/>
@@ -17924,7 +18139,11 @@
         </is>
       </c>
       <c r="K318" s="7" t="inlineStr"/>
-      <c r="L318" s="7" t="n"/>
+      <c r="L318" s="7" t="inlineStr">
+        <is>
+          <t>A1779057902[추정, 해외 공용 품번], A2479054303[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M318" s="7" t="inlineStr"/>
       <c r="N318" s="10" t="inlineStr">
         <is>
@@ -17933,7 +18152,7 @@
       </c>
       <c r="O318" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL)</t>
+          <t>ebay(2020-2025 GLB 순정 키), autoevolution(2024 GLB35 FL), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: W177 A클래스 2019 A1779057902·W247 A2479054303, HELLA 제조 키리스고) — 같은 MFA2 플랫폼(A·B·CLA·GLA·GLB) 키 기준 추정</t>
         </is>
       </c>
       <c r="P318" s="10" t="n"/>
@@ -18844,7 +19063,11 @@
         </is>
       </c>
       <c r="K334" s="7" t="inlineStr"/>
-      <c r="L334" s="7" t="n"/>
+      <c r="L334" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M334" s="7" t="inlineStr"/>
       <c r="N334" s="7" t="inlineStr">
         <is>
@@ -18853,7 +19076,7 @@
       </c>
       <c r="O334" s="7" t="inlineStr">
         <is>
-          <t>mbusa(GLC 2023-03 X254 SmartKey)</t>
+          <t>mbusa(GLC 2023-03 X254 SmartKey), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P334" s="7" t="inlineStr"/>
@@ -18894,7 +19117,11 @@
         </is>
       </c>
       <c r="K335" s="7" t="inlineStr"/>
-      <c r="L335" s="7" t="n"/>
+      <c r="L335" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M335" s="7" t="inlineStr"/>
       <c r="N335" s="7" t="inlineStr">
         <is>
@@ -18903,7 +19130,7 @@
       </c>
       <c r="O335" s="7" t="inlineStr">
         <is>
-          <t>mbworld(X254 디지털 키 미지원)</t>
+          <t>mbworld(X254 디지털 키 미지원), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P335" s="7" t="inlineStr"/>
@@ -18944,7 +19171,11 @@
         </is>
       </c>
       <c r="K336" s="7" t="inlineStr"/>
-      <c r="L336" s="7" t="n"/>
+      <c r="L336" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M336" s="7" t="inlineStr"/>
       <c r="N336" s="7" t="inlineStr">
         <is>
@@ -18953,7 +19184,7 @@
       </c>
       <c r="O336" s="7" t="inlineStr">
         <is>
-          <t>mbworld(2025 GLC 디지털 키 사전 장착), mbusa(GLC 2025-10 디지털 차키)</t>
+          <t>mbworld(2025 GLC 디지털 키 사전 장착), mbusa(GLC 2025-10 디지털 차키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P336" s="7" t="inlineStr"/>
@@ -18994,7 +19225,11 @@
         </is>
       </c>
       <c r="K337" s="7" t="inlineStr"/>
-      <c r="L337" s="7" t="n"/>
+      <c r="L337" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M337" s="7" t="inlineStr"/>
       <c r="N337" s="7" t="inlineStr">
         <is>
@@ -19003,7 +19238,7 @@
       </c>
       <c r="O337" s="7" t="inlineStr">
         <is>
-          <t>mbusa(GLC 2026-06 디지털 차키)</t>
+          <t>mbusa(GLC 2026-06 디지털 차키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P337" s="7" t="inlineStr"/>
@@ -19450,7 +19685,11 @@
         </is>
       </c>
       <c r="K345" s="7" t="inlineStr"/>
-      <c r="L345" s="7" t="n"/>
+      <c r="L345" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M345" s="7" t="inlineStr"/>
       <c r="N345" s="7" t="inlineStr">
         <is>
@@ -19459,7 +19698,7 @@
       </c>
       <c r="O345" s="7" t="inlineStr">
         <is>
-          <t>mbusa(2025 AMG GLC63 S E), mbworld(X254 디지털 키)</t>
+          <t>mbusa(2025 AMG GLC63 S E), mbworld(X254 디지털 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P345" s="7" t="inlineStr"/>
@@ -19500,7 +19739,11 @@
         </is>
       </c>
       <c r="K346" s="7" t="inlineStr"/>
-      <c r="L346" s="7" t="n"/>
+      <c r="L346" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M346" s="7" t="inlineStr"/>
       <c r="N346" s="7" t="inlineStr">
         <is>
@@ -19509,7 +19752,7 @@
       </c>
       <c r="O346" s="7" t="inlineStr">
         <is>
-          <t>mbusa(2025 AMG GLC63 S E), mbworld(X254 디지털 키)</t>
+          <t>mbusa(2025 AMG GLC63 S E), mbworld(X254 디지털 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P346" s="7" t="inlineStr"/>
@@ -19550,7 +19793,11 @@
         </is>
       </c>
       <c r="K347" s="7" t="inlineStr"/>
-      <c r="L347" s="7" t="n"/>
+      <c r="L347" s="7" t="inlineStr">
+        <is>
+          <t>A2069057403[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M347" s="7" t="inlineStr"/>
       <c r="N347" s="10" t="inlineStr">
         <is>
@@ -19559,7 +19806,7 @@
       </c>
       <c r="O347" s="7" t="inlineStr">
         <is>
-          <t>mbusa(2025 AMG GLC63 S E), mbworld(X254 디지털 키)</t>
+          <t>mbusa(2025 AMG GLC63 S E), mbworld(X254 디지털 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: C클래스 W206 2020+ A2069057403 HU64 키리스고) — 같은 MRA2 플랫폼(W206·W214·X254·C236) 키 기준 추정</t>
         </is>
       </c>
       <c r="P347" s="10" t="n"/>
@@ -22338,7 +22585,11 @@
         </is>
       </c>
       <c r="K397" s="7" t="inlineStr"/>
-      <c r="L397" s="7" t="n"/>
+      <c r="L397" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M397" s="7" t="inlineStr"/>
       <c r="N397" s="7" t="inlineStr">
         <is>
@@ -22347,7 +22598,7 @@
       </c>
       <c r="O397" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2026 GLS450 X167 순정 키), auto-data(X167 FL 2023)</t>
+          <t>ebay(2020-2026 GLS450 X167 순정 키), auto-data(X167 FL 2023), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P397" s="7" t="inlineStr"/>
@@ -22388,7 +22639,11 @@
         </is>
       </c>
       <c r="K398" s="7" t="inlineStr"/>
-      <c r="L398" s="7" t="n"/>
+      <c r="L398" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M398" s="7" t="inlineStr"/>
       <c r="N398" s="7" t="inlineStr">
         <is>
@@ -22397,7 +22652,7 @@
       </c>
       <c r="O398" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2026 GLS450 X167 순정 키), auto-data(X167 FL 2023)</t>
+          <t>ebay(2020-2026 GLS450 X167 순정 키), auto-data(X167 FL 2023), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P398" s="7" t="inlineStr"/>
@@ -22438,7 +22693,11 @@
         </is>
       </c>
       <c r="K399" s="7" t="inlineStr"/>
-      <c r="L399" s="7" t="n"/>
+      <c r="L399" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M399" s="7" t="inlineStr"/>
       <c r="N399" s="7" t="inlineStr">
         <is>
@@ -22447,7 +22706,7 @@
       </c>
       <c r="O399" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2026 GLS450 X167 순정 키), auto-data(X167 FL 2023)</t>
+          <t>ebay(2020-2026 GLS450 X167 순정 키), auto-data(X167 FL 2023), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P399" s="7" t="inlineStr"/>
@@ -22488,7 +22747,11 @@
         </is>
       </c>
       <c r="K400" s="7" t="inlineStr"/>
-      <c r="L400" s="7" t="n"/>
+      <c r="L400" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M400" s="7" t="inlineStr"/>
       <c r="N400" s="7" t="inlineStr">
         <is>
@@ -22497,7 +22760,7 @@
       </c>
       <c r="O400" s="7" t="inlineStr">
         <is>
-          <t>ebay(2020-2026 GLS450 X167 순정 키), auto-data(X167 FL 2023)</t>
+          <t>ebay(2020-2026 GLS450 X167 순정 키), auto-data(X167 FL 2023), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P400" s="7" t="inlineStr"/>
@@ -22538,7 +22801,11 @@
         </is>
       </c>
       <c r="K401" s="7" t="inlineStr"/>
-      <c r="L401" s="7" t="n"/>
+      <c r="L401" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M401" s="7" t="inlineStr"/>
       <c r="N401" s="7" t="inlineStr">
         <is>
@@ -22547,7 +22814,7 @@
       </c>
       <c r="O401" s="7" t="inlineStr">
         <is>
-          <t>mbusa(GLS 2026-07 디지털 차키), ebay(2020-2026 GLS450 키)</t>
+          <t>mbusa(GLS 2026-07 디지털 차키), ebay(2020-2026 GLS450 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P401" s="7" t="inlineStr"/>
@@ -22588,7 +22855,11 @@
         </is>
       </c>
       <c r="K402" s="7" t="inlineStr"/>
-      <c r="L402" s="7" t="n"/>
+      <c r="L402" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M402" s="7" t="inlineStr"/>
       <c r="N402" s="7" t="inlineStr">
         <is>
@@ -22597,7 +22868,7 @@
       </c>
       <c r="O402" s="7" t="inlineStr">
         <is>
-          <t>mbusa(GLS 2026-07 디지털 차키), ebay(2020-2026 GLS450 키)</t>
+          <t>mbusa(GLS 2026-07 디지털 차키), ebay(2020-2026 GLS450 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P402" s="7" t="inlineStr"/>
@@ -22638,7 +22909,11 @@
         </is>
       </c>
       <c r="K403" s="7" t="inlineStr"/>
-      <c r="L403" s="7" t="n"/>
+      <c r="L403" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M403" s="7" t="inlineStr"/>
       <c r="N403" s="7" t="inlineStr">
         <is>
@@ -22647,7 +22922,7 @@
       </c>
       <c r="O403" s="7" t="inlineStr">
         <is>
-          <t>mbusa(GLS 2026-07 디지털 차키), ebay(2020-2026 GLS450 키)</t>
+          <t>mbusa(GLS 2026-07 디지털 차키), ebay(2020-2026 GLS450 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P403" s="7" t="inlineStr"/>
@@ -22688,7 +22963,11 @@
         </is>
       </c>
       <c r="K404" s="7" t="inlineStr"/>
-      <c r="L404" s="7" t="n"/>
+      <c r="L404" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M404" s="7" t="inlineStr"/>
       <c r="N404" s="7" t="inlineStr">
         <is>
@@ -22697,7 +22976,7 @@
       </c>
       <c r="O404" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key)</t>
+          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P404" s="7" t="inlineStr"/>
@@ -22738,7 +23017,11 @@
         </is>
       </c>
       <c r="K405" s="7" t="inlineStr"/>
-      <c r="L405" s="7" t="n"/>
+      <c r="L405" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M405" s="7" t="inlineStr"/>
       <c r="N405" s="7" t="inlineStr">
         <is>
@@ -22747,7 +23030,7 @@
       </c>
       <c r="O405" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key)</t>
+          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P405" s="7" t="inlineStr"/>
@@ -22788,7 +23071,11 @@
         </is>
       </c>
       <c r="K406" s="7" t="inlineStr"/>
-      <c r="L406" s="7" t="n"/>
+      <c r="L406" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M406" s="7" t="inlineStr"/>
       <c r="N406" s="7" t="inlineStr">
         <is>
@@ -22797,7 +23084,7 @@
       </c>
       <c r="O406" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key)</t>
+          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P406" s="7" t="inlineStr"/>
@@ -22838,7 +23125,11 @@
         </is>
       </c>
       <c r="K407" s="7" t="inlineStr"/>
-      <c r="L407" s="7" t="n"/>
+      <c r="L407" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M407" s="7" t="inlineStr"/>
       <c r="N407" s="7" t="inlineStr">
         <is>
@@ -22847,7 +23138,7 @@
       </c>
       <c r="O407" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key)</t>
+          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P407" s="7" t="inlineStr"/>
@@ -22888,7 +23179,11 @@
         </is>
       </c>
       <c r="K408" s="7" t="inlineStr"/>
-      <c r="L408" s="7" t="n"/>
+      <c r="L408" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M408" s="7" t="inlineStr"/>
       <c r="N408" s="7" t="inlineStr">
         <is>
@@ -22897,7 +23192,7 @@
       </c>
       <c r="O408" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key)</t>
+          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P408" s="7" t="inlineStr"/>
@@ -22938,7 +23233,11 @@
         </is>
       </c>
       <c r="K409" s="7" t="inlineStr"/>
-      <c r="L409" s="7" t="n"/>
+      <c r="L409" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M409" s="7" t="inlineStr"/>
       <c r="N409" s="7" t="inlineStr">
         <is>
@@ -22947,7 +23246,7 @@
       </c>
       <c r="O409" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key)</t>
+          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P409" s="7" t="inlineStr"/>
@@ -22988,7 +23287,11 @@
         </is>
       </c>
       <c r="K410" s="7" t="inlineStr"/>
-      <c r="L410" s="7" t="n"/>
+      <c r="L410" s="7" t="inlineStr">
+        <is>
+          <t>A1679053303[추정, 해외 공용 품번], A1679054203[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M410" s="7" t="inlineStr"/>
       <c r="N410" s="7" t="inlineStr">
         <is>
@@ -22997,7 +23300,7 @@
       </c>
       <c r="O410" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key)</t>
+          <t>carinterior.alibaba(마이바흐 키), facebook(Maybach GLS600 auto key), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: FBS4 A1679053303·A1679054203 HU64 키리스고) — GLE(W167)와 같은 MHA 플랫폼 키 기준 추정</t>
         </is>
       </c>
       <c r="P410" s="7" t="inlineStr"/>
@@ -28246,7 +28549,11 @@
         </is>
       </c>
       <c r="K507" s="7" t="inlineStr"/>
-      <c r="L507" s="7" t="n"/>
+      <c r="L507" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M507" s="7" t="inlineStr"/>
       <c r="N507" s="7" t="inlineStr">
         <is>
@@ -28255,7 +28562,7 @@
       </c>
       <c r="O507" s="7" t="inlineStr">
         <is>
-          <t>wikipedia(EQS 2021.5 생산)</t>
+          <t>wikipedia(EQS 2021.5 생산), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P507" s="7" t="inlineStr"/>
@@ -28296,7 +28603,11 @@
         </is>
       </c>
       <c r="K508" s="7" t="inlineStr"/>
-      <c r="L508" s="7" t="n"/>
+      <c r="L508" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M508" s="7" t="inlineStr"/>
       <c r="N508" s="7" t="inlineStr">
         <is>
@@ -28305,7 +28616,7 @@
       </c>
       <c r="O508" s="7" t="inlineStr">
         <is>
-          <t>ebay(2022-2023 EQS 키 IYZ-MS5 미국형 — 제외)</t>
+          <t>ebay(2022-2023 EQS 키 IYZ-MS5 미국형 — 제외), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P508" s="7" t="inlineStr"/>
@@ -28346,7 +28657,11 @@
         </is>
       </c>
       <c r="K509" s="7" t="inlineStr"/>
-      <c r="L509" s="7" t="n"/>
+      <c r="L509" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M509" s="7" t="inlineStr"/>
       <c r="N509" s="7" t="inlineStr">
         <is>
@@ -28355,7 +28670,7 @@
       </c>
       <c r="O509" s="7" t="inlineStr">
         <is>
-          <t>mbworld(EQS 디지털 키 CY23/2부터)</t>
+          <t>mbworld(EQS 디지털 키 CY23/2부터), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P509" s="7" t="inlineStr"/>
@@ -28396,7 +28711,11 @@
         </is>
       </c>
       <c r="K510" s="7" t="inlineStr"/>
-      <c r="L510" s="7" t="n"/>
+      <c r="L510" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M510" s="7" t="inlineStr"/>
       <c r="N510" s="7" t="inlineStr">
         <is>
@@ -28405,7 +28724,7 @@
       </c>
       <c r="O510" s="7" t="inlineStr">
         <is>
-          <t>ecstuning(2024 EQS 키), mbusa(EQS 2024)</t>
+          <t>ecstuning(2024 EQS 키), mbusa(EQS 2024), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P510" s="7" t="inlineStr"/>
@@ -28446,7 +28765,11 @@
         </is>
       </c>
       <c r="K511" s="7" t="inlineStr"/>
-      <c r="L511" s="7" t="n"/>
+      <c r="L511" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M511" s="7" t="inlineStr"/>
       <c r="N511" s="7" t="inlineStr">
         <is>
@@ -28455,7 +28778,7 @@
       </c>
       <c r="O511" s="7" t="inlineStr">
         <is>
-          <t>ebay(20-25 EQS 키)</t>
+          <t>ebay(20-25 EQS 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P511" s="7" t="inlineStr"/>
@@ -28496,7 +28819,11 @@
         </is>
       </c>
       <c r="K512" s="7" t="inlineStr"/>
-      <c r="L512" s="7" t="n"/>
+      <c r="L512" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M512" s="7" t="inlineStr"/>
       <c r="N512" s="7" t="inlineStr">
         <is>
@@ -28505,7 +28832,7 @@
       </c>
       <c r="O512" s="7" t="inlineStr">
         <is>
-          <t>carinterior.alibaba(2026 MRA II 키 CR2032)</t>
+          <t>carinterior.alibaba(2026 MRA II 키 CR2032), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P512" s="7" t="inlineStr"/>
@@ -28546,7 +28873,11 @@
         </is>
       </c>
       <c r="K513" s="7" t="inlineStr"/>
-      <c r="L513" s="7" t="n"/>
+      <c r="L513" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M513" s="7" t="inlineStr"/>
       <c r="N513" s="7" t="inlineStr">
         <is>
@@ -28555,7 +28886,7 @@
       </c>
       <c r="O513" s="7" t="inlineStr">
         <is>
-          <t>wikipedia(EQE)</t>
+          <t>wikipedia(EQE), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P513" s="7" t="inlineStr"/>
@@ -28596,7 +28927,11 @@
         </is>
       </c>
       <c r="K514" s="7" t="inlineStr"/>
-      <c r="L514" s="7" t="n"/>
+      <c r="L514" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M514" s="7" t="inlineStr"/>
       <c r="N514" s="7" t="inlineStr">
         <is>
@@ -28605,7 +28940,7 @@
       </c>
       <c r="O514" s="7" t="inlineStr">
         <is>
-          <t>mbworld(EQE digital key)</t>
+          <t>mbworld(EQE digital key), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P514" s="7" t="inlineStr"/>
@@ -28646,7 +28981,11 @@
         </is>
       </c>
       <c r="K515" s="7" t="inlineStr"/>
-      <c r="L515" s="7" t="n"/>
+      <c r="L515" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M515" s="7" t="inlineStr"/>
       <c r="N515" s="7" t="inlineStr">
         <is>
@@ -28655,7 +28994,7 @@
       </c>
       <c r="O515" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQE 2024-09 디지털 차키)</t>
+          <t>mbusa(EQE 2024-09 디지털 차키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P515" s="7" t="inlineStr"/>
@@ -28696,7 +29035,11 @@
         </is>
       </c>
       <c r="K516" s="7" t="inlineStr"/>
-      <c r="L516" s="7" t="n"/>
+      <c r="L516" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M516" s="7" t="inlineStr"/>
       <c r="N516" s="7" t="inlineStr">
         <is>
@@ -28705,7 +29048,7 @@
       </c>
       <c r="O516" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQE 디지털 차키)</t>
+          <t>mbusa(EQE 디지털 차키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P516" s="7" t="inlineStr"/>
@@ -28746,14 +29089,22 @@
         </is>
       </c>
       <c r="K517" s="7" t="inlineStr"/>
-      <c r="L517" s="7" t="n"/>
+      <c r="L517" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M517" s="7" t="inlineStr"/>
       <c r="N517" s="10" t="inlineStr">
         <is>
           <t>EIS</t>
         </is>
       </c>
-      <c r="O517" s="7" t="inlineStr"/>
+      <c r="O517" s="7" t="inlineStr">
+        <is>
+          <t>auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
+        </is>
+      </c>
       <c r="P517" s="10" t="n"/>
     </row>
     <row r="518">
@@ -28792,7 +29143,11 @@
         </is>
       </c>
       <c r="K518" s="7" t="inlineStr"/>
-      <c r="L518" s="7" t="n"/>
+      <c r="L518" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M518" s="7" t="inlineStr"/>
       <c r="N518" s="7" t="inlineStr">
         <is>
@@ -28801,7 +29156,7 @@
       </c>
       <c r="O518" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQS SUV 2023-01·2024-02 디지털 차키), amazon(2023-2026 EQS SUV 3버튼 키)</t>
+          <t>mbusa(EQS SUV 2023-01·2024-02 디지털 차키), amazon(2023-2026 EQS SUV 3버튼 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P518" s="7" t="inlineStr"/>
@@ -28842,7 +29197,11 @@
         </is>
       </c>
       <c r="K519" s="7" t="inlineStr"/>
-      <c r="L519" s="7" t="n"/>
+      <c r="L519" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M519" s="7" t="inlineStr"/>
       <c r="N519" s="7" t="inlineStr">
         <is>
@@ -28851,7 +29210,7 @@
       </c>
       <c r="O519" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQS SUV 2023-01·2024-02 디지털 차키), amazon(2023-2026 EQS SUV 3버튼 키)</t>
+          <t>mbusa(EQS SUV 2023-01·2024-02 디지털 차키), amazon(2023-2026 EQS SUV 3버튼 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P519" s="7" t="inlineStr"/>
@@ -28892,7 +29251,11 @@
         </is>
       </c>
       <c r="K520" s="7" t="inlineStr"/>
-      <c r="L520" s="7" t="n"/>
+      <c r="L520" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M520" s="7" t="inlineStr"/>
       <c r="N520" s="7" t="inlineStr">
         <is>
@@ -28901,7 +29264,7 @@
       </c>
       <c r="O520" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQS SUV 2023-01·2024-02 디지털 차키), amazon(2023-2026 EQS SUV 3버튼 키)</t>
+          <t>mbusa(EQS SUV 2023-01·2024-02 디지털 차키), amazon(2023-2026 EQS SUV 3버튼 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P520" s="7" t="inlineStr"/>
@@ -28942,7 +29305,11 @@
         </is>
       </c>
       <c r="K521" s="7" t="inlineStr"/>
-      <c r="L521" s="7" t="n"/>
+      <c r="L521" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M521" s="7" t="inlineStr"/>
       <c r="N521" s="7" t="inlineStr">
         <is>
@@ -28951,7 +29318,7 @@
       </c>
       <c r="O521" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQS SUV 2023-01·2024-02 디지털 차키), amazon(2023-2026 EQS SUV 3버튼 키)</t>
+          <t>mbusa(EQS SUV 2023-01·2024-02 디지털 차키), amazon(2023-2026 EQS SUV 3버튼 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P521" s="7" t="inlineStr"/>
@@ -28992,7 +29359,11 @@
         </is>
       </c>
       <c r="K522" s="7" t="inlineStr"/>
-      <c r="L522" s="7" t="n"/>
+      <c r="L522" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M522" s="7" t="inlineStr"/>
       <c r="N522" s="7" t="inlineStr">
         <is>
@@ -29001,7 +29372,7 @@
       </c>
       <c r="O522" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQE SUV 2024-03 디지털 차키), amazon(2023-2026 EQE SUV 3버튼 키)</t>
+          <t>mbusa(EQE SUV 2024-03 디지털 차키), amazon(2023-2026 EQE SUV 3버튼 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P522" s="7" t="inlineStr"/>
@@ -29042,7 +29413,11 @@
         </is>
       </c>
       <c r="K523" s="7" t="inlineStr"/>
-      <c r="L523" s="7" t="n"/>
+      <c r="L523" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M523" s="7" t="inlineStr"/>
       <c r="N523" s="7" t="inlineStr">
         <is>
@@ -29051,7 +29426,7 @@
       </c>
       <c r="O523" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQE SUV 2024-03 디지털 차키), amazon(2023-2026 EQE SUV 3버튼 키)</t>
+          <t>mbusa(EQE SUV 2024-03 디지털 차키), amazon(2023-2026 EQE SUV 3버튼 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P523" s="7" t="inlineStr"/>
@@ -29092,7 +29467,11 @@
         </is>
       </c>
       <c r="K524" s="7" t="inlineStr"/>
-      <c r="L524" s="7" t="n"/>
+      <c r="L524" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M524" s="7" t="inlineStr"/>
       <c r="N524" s="7" t="inlineStr">
         <is>
@@ -29101,7 +29480,7 @@
       </c>
       <c r="O524" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQE SUV 2024-03 디지털 차키), amazon(2023-2026 EQE SUV 3버튼 키)</t>
+          <t>mbusa(EQE SUV 2024-03 디지털 차키), amazon(2023-2026 EQE SUV 3버튼 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P524" s="7" t="inlineStr"/>
@@ -29142,7 +29521,11 @@
         </is>
       </c>
       <c r="K525" s="7" t="inlineStr"/>
-      <c r="L525" s="7" t="n"/>
+      <c r="L525" s="7" t="inlineStr">
+        <is>
+          <t>A2239057507[추정, 해외 공용 품번], A2239054408[추정, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M525" s="7" t="inlineStr"/>
       <c r="N525" s="7" t="inlineStr">
         <is>
@@ -29151,7 +29534,7 @@
       </c>
       <c r="O525" s="7" t="inlineStr">
         <is>
-          <t>mbusa(EQE SUV 2024-03 디지털 차키), amazon(2023-2026 EQE SUV 3버튼 키)</t>
+          <t>mbusa(EQE SUV 2024-03 디지털 차키), amazon(2023-2026 EQE SUV 3버튼 키), auto-keys.eu(메르세데스 순정 스마트키 433.92MHz: S클래스 2020+ A2239057507·A2239054408) — S클래스(W223)와 같은 세대 키 기준 추정</t>
         </is>
       </c>
       <c r="P525" s="7" t="inlineStr"/>
@@ -29168,7 +29551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A55"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -29531,6 +29914,13 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>- 6차 세대별 보완: 2019년 이후 신형(EPC 범위 밖)은 같은 플랫폼 순정 433MHz 키 품번을 [추정]으로 기재 — MFA2(CLA·GLA·GLB) A1779057902·A2479054303, MRA2(W214·X254·C236) A2069057403, W223·EQS·EQE A2239057507·A2239054408, X167 A1679053303·A1679054203(auto-keys.eu)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
